--- a/datos.xlsx
+++ b/datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brio\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brio\Documents\Ley_de_Paschen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2497283B-91CC-40E6-8084-9ED003CDEE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57D3F9F-3CB7-4AD6-A9D0-AEEF8DA3D462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9C911C4F-B33B-4DF8-B6F9-252FC92448E8}"/>
   </bookViews>
@@ -69,12 +69,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -160,6 +166,13 @@
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E86A565-FB1F-4769-AA56-C12C3CCD5044}">
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1295,7 +1308,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>46262</v>
       </c>
@@ -1312,7 +1325,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>46262</v>
       </c>
@@ -1329,7 +1342,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>46262</v>
       </c>
@@ -1346,7 +1359,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>46262</v>
       </c>
@@ -1363,7 +1376,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>46262</v>
       </c>
@@ -1380,7 +1393,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>46262</v>
       </c>
@@ -1397,7 +1410,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>46262</v>
       </c>
@@ -1414,7 +1427,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>46262</v>
       </c>
@@ -1430,10 +1443,8 @@
       <c r="E56" s="2">
         <v>326</v>
       </c>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>46262</v>
       </c>
@@ -1449,10 +1460,8 @@
       <c r="E57" s="2">
         <v>458</v>
       </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>46262</v>
       </c>
@@ -1468,10 +1477,8 @@
       <c r="E58" s="2">
         <v>360</v>
       </c>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>46262</v>
       </c>
@@ -1487,10 +1494,8 @@
       <c r="E59" s="2">
         <v>329</v>
       </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>46262</v>
       </c>
@@ -1506,10 +1511,8 @@
       <c r="E60" s="2">
         <v>314</v>
       </c>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-    </row>
-    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>46262</v>
       </c>
@@ -1525,10 +1528,8 @@
       <c r="E61" s="2">
         <v>308</v>
       </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>46262</v>
       </c>
@@ -1544,10 +1545,8 @@
       <c r="E62" s="2">
         <v>305</v>
       </c>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-    </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>46262</v>
       </c>
@@ -1563,10 +1562,8 @@
       <c r="E63" s="2">
         <v>304</v>
       </c>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>46262</v>
       </c>
@@ -1582,10 +1579,8 @@
       <c r="E64" s="2">
         <v>306</v>
       </c>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>46262</v>
       </c>
@@ -1601,10 +1596,8 @@
       <c r="E65" s="2">
         <v>307</v>
       </c>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>46262</v>
       </c>
@@ -1620,10 +1613,8 @@
       <c r="E66" s="2">
         <v>308</v>
       </c>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>46262</v>
       </c>
@@ -1639,10 +1630,8 @@
       <c r="E67" s="2">
         <v>314</v>
       </c>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>46262</v>
       </c>
@@ -1658,10 +1647,8 @@
       <c r="E68" s="2">
         <v>326</v>
       </c>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>46262</v>
       </c>
@@ -1677,10 +1664,8 @@
       <c r="E69" s="2">
         <v>328</v>
       </c>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>46262</v>
       </c>
@@ -1696,10 +1681,8 @@
       <c r="E70" s="2">
         <v>329</v>
       </c>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>46262</v>
       </c>
@@ -1715,10 +1698,8 @@
       <c r="E71" s="2">
         <v>330</v>
       </c>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>46262</v>
       </c>
@@ -1734,10 +1715,8 @@
       <c r="E72" s="2">
         <v>427</v>
       </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-    </row>
-    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>46262</v>
       </c>
@@ -1753,10 +1732,8 @@
       <c r="E73" s="2">
         <v>410</v>
       </c>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>46262</v>
       </c>
@@ -1772,10 +1749,8 @@
       <c r="E74" s="2">
         <v>395</v>
       </c>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>46262</v>
       </c>
@@ -1791,10 +1766,8 @@
       <c r="E75" s="2">
         <v>381</v>
       </c>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>46262</v>
       </c>
@@ -1810,10 +1783,8 @@
       <c r="E76" s="2">
         <v>346</v>
       </c>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>46262</v>
       </c>
@@ -1829,10 +1800,8 @@
       <c r="E77" s="2">
         <v>327</v>
       </c>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-    </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>46262</v>
       </c>
@@ -1848,10 +1817,8 @@
       <c r="E78" s="2">
         <v>311</v>
       </c>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-    </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>46262</v>
       </c>
@@ -1867,10 +1834,8 @@
       <c r="E79" s="2">
         <v>308</v>
       </c>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>46262</v>
       </c>
@@ -1886,10 +1851,8 @@
       <c r="E80" s="2">
         <v>308</v>
       </c>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>46262</v>
       </c>
@@ -1905,10 +1868,8 @@
       <c r="E81" s="2">
         <v>309</v>
       </c>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>46262</v>
       </c>
@@ -1924,10 +1885,8 @@
       <c r="E82" s="2">
         <v>328</v>
       </c>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>46262</v>
       </c>
@@ -1943,10 +1902,8 @@
       <c r="E83" s="2">
         <v>328</v>
       </c>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-    </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>46262</v>
       </c>
@@ -1962,10 +1919,8 @@
       <c r="E84" s="2">
         <v>329</v>
       </c>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>46262</v>
       </c>
@@ -1981,10 +1936,8 @@
       <c r="E85" s="2">
         <v>329</v>
       </c>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>46262</v>
       </c>
@@ -2000,8 +1953,2268 @@
       <c r="E86" s="2">
         <v>333</v>
       </c>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B87" s="1">
+        <v>25</v>
+      </c>
+      <c r="C87" s="4">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="D87" s="1">
+        <v>469</v>
+      </c>
+      <c r="E87" s="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B88" s="2">
+        <v>25</v>
+      </c>
+      <c r="C88" s="5">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="D88" s="2">
+        <v>435</v>
+      </c>
+      <c r="E88" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B89" s="2">
+        <v>25</v>
+      </c>
+      <c r="C89" s="5">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="D89" s="2">
+        <v>418</v>
+      </c>
+      <c r="E89" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B90" s="2">
+        <v>25</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="D90" s="2">
+        <v>384</v>
+      </c>
+      <c r="E90" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B91" s="2">
+        <v>25</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D91" s="2">
+        <v>367</v>
+      </c>
+      <c r="E91" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B92" s="2">
+        <v>25</v>
+      </c>
+      <c r="C92" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="D92" s="2">
+        <v>374</v>
+      </c>
+      <c r="E92" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B93" s="2">
+        <v>25</v>
+      </c>
+      <c r="C93" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="D93" s="2">
+        <v>382</v>
+      </c>
+      <c r="E93" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B94" s="2">
+        <v>25</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D94" s="2">
+        <v>401</v>
+      </c>
+      <c r="E94" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B95" s="2">
+        <v>25</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="D95" s="2">
+        <v>410</v>
+      </c>
+      <c r="E95" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B96" s="2">
+        <v>25</v>
+      </c>
+      <c r="C96" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="D96" s="2">
+        <v>427</v>
+      </c>
+      <c r="E96" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B97" s="2">
+        <v>25</v>
+      </c>
+      <c r="C97" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="D97" s="2">
+        <v>467</v>
+      </c>
+      <c r="E97" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B98" s="2">
+        <v>25</v>
+      </c>
+      <c r="C98" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D98" s="2">
+        <v>490</v>
+      </c>
+      <c r="E98" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B99" s="2">
+        <v>25</v>
+      </c>
+      <c r="C99" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="D99" s="2">
+        <v>508</v>
+      </c>
+      <c r="E99" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B100" s="2">
+        <v>25</v>
+      </c>
+      <c r="C100" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D100" s="2">
+        <v>541</v>
+      </c>
+      <c r="E100" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B101" s="2">
+        <v>25</v>
+      </c>
+      <c r="C101" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="D101" s="2">
+        <v>574</v>
+      </c>
+      <c r="E101" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B102" s="2">
+        <v>30</v>
+      </c>
+      <c r="C102" s="5">
+        <v>6.2E-2</v>
+      </c>
+      <c r="D102" s="2">
+        <v>455</v>
+      </c>
+      <c r="E102" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B103" s="2">
+        <v>30</v>
+      </c>
+      <c r="C103" s="5">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D103" s="2">
+        <v>426</v>
+      </c>
+      <c r="E103" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B104" s="2">
+        <v>30</v>
+      </c>
+      <c r="C104" s="5">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="D104" s="2">
+        <v>394</v>
+      </c>
+      <c r="E104" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B105" s="2">
+        <v>30</v>
+      </c>
+      <c r="C105" s="5">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="D105" s="2">
+        <v>385</v>
+      </c>
+      <c r="E105" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B106" s="2">
+        <v>30</v>
+      </c>
+      <c r="C106" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D106" s="2">
+        <v>379</v>
+      </c>
+      <c r="E106" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B107" s="2">
+        <v>30</v>
+      </c>
+      <c r="C107" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="D107" s="2">
+        <v>363</v>
+      </c>
+      <c r="E107" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B108" s="2">
+        <v>30</v>
+      </c>
+      <c r="C108" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D108" s="2">
+        <v>368</v>
+      </c>
+      <c r="E108" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B109" s="2">
+        <v>30</v>
+      </c>
+      <c r="C109" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D109" s="2">
+        <v>384</v>
+      </c>
+      <c r="E109" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B110" s="2">
+        <v>30</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="D110" s="2">
+        <v>419</v>
+      </c>
+      <c r="E110" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B111" s="2">
+        <v>30</v>
+      </c>
+      <c r="C111" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D111" s="2">
+        <v>462</v>
+      </c>
+      <c r="E111" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B112" s="2">
+        <v>30</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="D112" s="2">
+        <v>506</v>
+      </c>
+      <c r="E112" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B113" s="2">
+        <v>30</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="D113" s="2">
+        <v>532</v>
+      </c>
+      <c r="E113" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B114" s="2">
+        <v>30</v>
+      </c>
+      <c r="C114" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D114" s="2">
+        <v>570</v>
+      </c>
+      <c r="E114" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B115" s="1">
+        <v>35</v>
+      </c>
+      <c r="C115" s="4">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D115" s="1">
+        <v>557</v>
+      </c>
+      <c r="E115" s="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="2">
+        <v>35</v>
+      </c>
+      <c r="C116" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D116" s="2">
+        <v>531</v>
+      </c>
+      <c r="E116" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B117" s="2">
+        <v>35</v>
+      </c>
+      <c r="C117" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="D117" s="2">
+        <v>496</v>
+      </c>
+      <c r="E117" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B118" s="2">
+        <v>35</v>
+      </c>
+      <c r="C118" s="5">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D118" s="2">
+        <v>434</v>
+      </c>
+      <c r="E118" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B119" s="2">
+        <v>35</v>
+      </c>
+      <c r="C119" s="5">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="D119" s="2">
+        <v>409</v>
+      </c>
+      <c r="E119" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B120" s="2">
+        <v>35</v>
+      </c>
+      <c r="C120" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="D120" s="2">
+        <v>379</v>
+      </c>
+      <c r="E120" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B121" s="12">
+        <v>35</v>
+      </c>
+      <c r="C121" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="D121" s="12">
+        <v>373</v>
+      </c>
+      <c r="E121" s="12">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B122" s="2">
+        <v>35</v>
+      </c>
+      <c r="C122" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D122" s="2">
+        <v>374</v>
+      </c>
+      <c r="E122" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B123" s="2">
+        <v>35</v>
+      </c>
+      <c r="C123" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D123" s="2">
+        <v>411</v>
+      </c>
+      <c r="E123" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B124" s="2">
+        <v>35</v>
+      </c>
+      <c r="C124" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="D124" s="2">
+        <v>447</v>
+      </c>
+      <c r="E124" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B125" s="2">
+        <v>35</v>
+      </c>
+      <c r="C125" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="D125" s="2">
+        <v>477</v>
+      </c>
+      <c r="E125" s="2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B126" s="2">
+        <v>35</v>
+      </c>
+      <c r="C126" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D126" s="2">
+        <v>531</v>
+      </c>
+      <c r="E126" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B127" s="2">
+        <v>35</v>
+      </c>
+      <c r="C127" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="D127" s="2">
+        <v>566</v>
+      </c>
+      <c r="E127" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B128" s="2">
+        <v>40</v>
+      </c>
+      <c r="C128" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D128" s="2">
+        <v>451</v>
+      </c>
+      <c r="E128" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B129" s="2">
+        <v>40</v>
+      </c>
+      <c r="C129" s="5">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="D129" s="2">
+        <v>454</v>
+      </c>
+      <c r="E129" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B130" s="2">
+        <v>40</v>
+      </c>
+      <c r="C130" s="5">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="D130" s="2">
+        <v>437</v>
+      </c>
+      <c r="E130" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B131" s="2">
+        <v>40</v>
+      </c>
+      <c r="C131" s="5">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="D131" s="2">
+        <v>406</v>
+      </c>
+      <c r="E131" s="2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B132" s="2">
+        <v>40</v>
+      </c>
+      <c r="C132" s="5">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D132" s="2">
+        <v>420</v>
+      </c>
+      <c r="E132" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B133" s="2">
+        <v>40</v>
+      </c>
+      <c r="C133" s="5">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="D133" s="2">
+        <v>396</v>
+      </c>
+      <c r="E133" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B134" s="12">
+        <v>40</v>
+      </c>
+      <c r="C134" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="D134" s="12">
+        <v>370</v>
+      </c>
+      <c r="E134" s="12">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B135" s="2">
+        <v>40</v>
+      </c>
+      <c r="C135" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D135" s="2">
+        <v>393</v>
+      </c>
+      <c r="E135" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B136" s="2">
+        <v>40</v>
+      </c>
+      <c r="C136" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D136" s="2">
+        <v>440</v>
+      </c>
+      <c r="E136" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B137" s="2">
+        <v>40</v>
+      </c>
+      <c r="C137" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D137" s="2">
+        <v>453</v>
+      </c>
+      <c r="E137" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B138" s="2">
+        <v>40</v>
+      </c>
+      <c r="C138" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="D138" s="2">
+        <v>489</v>
+      </c>
+      <c r="E138" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B139" s="2">
+        <v>40</v>
+      </c>
+      <c r="C139" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="D139" s="2">
+        <v>550</v>
+      </c>
+      <c r="E139" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B140" s="2">
+        <v>40</v>
+      </c>
+      <c r="C140" s="5">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="D140" s="2">
+        <v>542</v>
+      </c>
+      <c r="E140" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B141" s="2">
+        <v>40</v>
+      </c>
+      <c r="C141" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D141" s="2">
+        <v>461</v>
+      </c>
+      <c r="E141" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B142" s="2">
+        <v>40</v>
+      </c>
+      <c r="C142" s="5">
+        <v>6.3E-2</v>
+      </c>
+      <c r="D142" s="2">
+        <v>420</v>
+      </c>
+      <c r="E142" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B143" s="2">
+        <v>40</v>
+      </c>
+      <c r="C143" s="5">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="D143" s="2">
+        <v>410</v>
+      </c>
+      <c r="E143" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B144" s="2">
+        <v>40</v>
+      </c>
+      <c r="C144" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="D144" s="2">
+        <v>410</v>
+      </c>
+      <c r="E144" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B145" s="2">
+        <v>40</v>
+      </c>
+      <c r="C145" s="5">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="D145" s="2">
+        <v>402</v>
+      </c>
+      <c r="E145" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B146" s="2">
+        <v>40</v>
+      </c>
+      <c r="C146" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>401</v>
+      </c>
+      <c r="E146" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B147" s="2">
+        <v>40</v>
+      </c>
+      <c r="C147" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D147" s="2">
+        <v>409</v>
+      </c>
+      <c r="E147" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B148" s="2">
+        <v>40</v>
+      </c>
+      <c r="C148" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="D148" s="2">
+        <v>451</v>
+      </c>
+      <c r="E148" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B149" s="2">
+        <v>40</v>
+      </c>
+      <c r="C149" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="D149" s="2">
+        <v>532</v>
+      </c>
+      <c r="E149" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B150" s="2">
+        <v>45</v>
+      </c>
+      <c r="C150" s="5">
+        <v>4.7E-2</v>
+      </c>
+      <c r="D150" s="2">
+        <v>557</v>
+      </c>
+      <c r="E150" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B151" s="2">
+        <v>45</v>
+      </c>
+      <c r="C151" s="5">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="D151" s="2">
+        <v>495</v>
+      </c>
+      <c r="E151" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B152" s="2">
+        <v>45</v>
+      </c>
+      <c r="C152" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="D152" s="2">
+        <v>460</v>
+      </c>
+      <c r="E152" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B153" s="12">
+        <v>45</v>
+      </c>
+      <c r="C153" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D153" s="12">
+        <v>424</v>
+      </c>
+      <c r="E153" s="12">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B154" s="2">
+        <v>45</v>
+      </c>
+      <c r="C154" s="5">
+        <v>7.8E-2</v>
+      </c>
+      <c r="D154" s="2">
+        <v>435</v>
+      </c>
+      <c r="E154" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B155" s="2">
+        <v>45</v>
+      </c>
+      <c r="C155" s="5">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="D155" s="2">
+        <v>451</v>
+      </c>
+      <c r="E155" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B156" s="2">
+        <v>45</v>
+      </c>
+      <c r="C156" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D156" s="2">
+        <v>408</v>
+      </c>
+      <c r="E156" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B157" s="2">
+        <v>45</v>
+      </c>
+      <c r="C157" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="D157" s="2">
+        <v>462</v>
+      </c>
+      <c r="E157" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B158" s="2">
+        <v>45</v>
+      </c>
+      <c r="C158" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="D158" s="2">
+        <v>503</v>
+      </c>
+      <c r="E158" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B159" s="2">
+        <v>25</v>
+      </c>
+      <c r="C159" s="5">
+        <v>7.8E-2</v>
+      </c>
+      <c r="D159" s="2">
+        <v>436</v>
+      </c>
+      <c r="E159" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B160" s="2">
+        <v>25</v>
+      </c>
+      <c r="C160" s="5">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="D160" s="2">
+        <v>426</v>
+      </c>
+      <c r="E160" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B161" s="2">
+        <v>25</v>
+      </c>
+      <c r="C161" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D161" s="2">
+        <v>398</v>
+      </c>
+      <c r="E161" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B162" s="12">
+        <v>25</v>
+      </c>
+      <c r="C162" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="D162" s="12">
+        <v>363</v>
+      </c>
+      <c r="E162" s="12">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B163" s="2">
+        <v>25</v>
+      </c>
+      <c r="C163" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D163" s="2">
+        <v>373</v>
+      </c>
+      <c r="E163" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B164" s="2">
+        <v>25</v>
+      </c>
+      <c r="C164" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D164" s="2">
+        <v>399</v>
+      </c>
+      <c r="E164" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B165" s="2">
+        <v>25</v>
+      </c>
+      <c r="C165" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="D165" s="2">
+        <v>450</v>
+      </c>
+      <c r="E165" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B166" s="2">
+        <v>25</v>
+      </c>
+      <c r="C166" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="D166" s="2">
+        <v>478</v>
+      </c>
+      <c r="E166" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B167" s="2">
+        <v>25</v>
+      </c>
+      <c r="C167" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="D167" s="2">
+        <v>510</v>
+      </c>
+      <c r="E167" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B168" s="2">
+        <v>25</v>
+      </c>
+      <c r="C168" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="D168" s="2">
+        <v>558</v>
+      </c>
+      <c r="E168" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B169" s="2">
+        <v>15</v>
+      </c>
+      <c r="C169" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="D169" s="2">
+        <v>516</v>
+      </c>
+      <c r="E169" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B170" s="2">
+        <v>15</v>
+      </c>
+      <c r="C170" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D170" s="2">
+        <v>403</v>
+      </c>
+      <c r="E170" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B171" s="2">
+        <v>15</v>
+      </c>
+      <c r="C171" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="D171" s="2">
+        <v>367</v>
+      </c>
+      <c r="E171" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B172" s="2">
+        <v>15</v>
+      </c>
+      <c r="C172" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D172" s="2">
+        <v>358</v>
+      </c>
+      <c r="E172" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B173" s="12">
+        <v>15</v>
+      </c>
+      <c r="C173" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="D173" s="12">
+        <v>348</v>
+      </c>
+      <c r="E173" s="12">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B174" s="2">
+        <v>15</v>
+      </c>
+      <c r="C174" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D174" s="2">
+        <v>358</v>
+      </c>
+      <c r="E174" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B175" s="2">
+        <v>15</v>
+      </c>
+      <c r="C175" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="D175" s="2">
+        <v>369</v>
+      </c>
+      <c r="E175" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B176" s="2">
+        <v>15</v>
+      </c>
+      <c r="C176" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="D176" s="2">
+        <v>403</v>
+      </c>
+      <c r="E176" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B177" s="2">
+        <v>15</v>
+      </c>
+      <c r="C177" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="D177" s="2">
+        <v>438</v>
+      </c>
+      <c r="E177" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B178" s="2">
+        <v>15</v>
+      </c>
+      <c r="C178" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D178" s="2">
+        <v>465</v>
+      </c>
+      <c r="E178" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B179" s="6">
+        <v>15</v>
+      </c>
+      <c r="C179" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="D179" s="6">
+        <v>501</v>
+      </c>
+      <c r="E179" s="6">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B180" s="2">
+        <v>5</v>
+      </c>
+      <c r="C180" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="D180" s="2">
+        <v>443</v>
+      </c>
+      <c r="E180" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B181" s="2">
+        <v>5</v>
+      </c>
+      <c r="C181" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D181" s="2">
+        <v>380</v>
+      </c>
+      <c r="E181" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B182" s="2">
+        <v>5</v>
+      </c>
+      <c r="C182" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="D182" s="2">
+        <v>369</v>
+      </c>
+      <c r="E182" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B183" s="2">
+        <v>5</v>
+      </c>
+      <c r="C183" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="D183" s="2">
+        <v>358</v>
+      </c>
+      <c r="E183" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B184" s="2">
+        <v>5</v>
+      </c>
+      <c r="C184" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="D184" s="2">
+        <v>346</v>
+      </c>
+      <c r="E184" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B185" s="12">
+        <v>5</v>
+      </c>
+      <c r="C185" s="13">
+        <v>0.72</v>
+      </c>
+      <c r="D185" s="12">
+        <v>339</v>
+      </c>
+      <c r="E185" s="12">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B186" s="2">
+        <v>5</v>
+      </c>
+      <c r="C186" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="D186" s="2">
+        <v>354</v>
+      </c>
+      <c r="E186" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B187" s="2">
+        <v>5</v>
+      </c>
+      <c r="C187" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="D187" s="2">
+        <v>353</v>
+      </c>
+      <c r="E187" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B188" s="2">
+        <v>5</v>
+      </c>
+      <c r="C188" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D188" s="2">
+        <v>361</v>
+      </c>
+      <c r="E188" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B189" s="2">
+        <v>5</v>
+      </c>
+      <c r="C189" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="D189" s="2">
+        <v>380</v>
+      </c>
+      <c r="E189" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B190" s="2">
+        <v>10</v>
+      </c>
+      <c r="C190" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="D190" s="2">
+        <v>476</v>
+      </c>
+      <c r="E190" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B191" s="2">
+        <v>10</v>
+      </c>
+      <c r="C191" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="D191" s="2">
+        <v>394</v>
+      </c>
+      <c r="E191" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B192" s="2">
+        <v>10</v>
+      </c>
+      <c r="C192" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D192" s="2">
+        <v>356</v>
+      </c>
+      <c r="E192" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B193" s="2">
+        <v>10</v>
+      </c>
+      <c r="C193" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="D193" s="2">
+        <v>354</v>
+      </c>
+      <c r="E193" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B194" s="2">
+        <v>10</v>
+      </c>
+      <c r="C194" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="D194" s="2">
+        <v>355</v>
+      </c>
+      <c r="E194" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B195" s="2">
+        <v>10</v>
+      </c>
+      <c r="C195" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D195" s="2">
+        <v>371</v>
+      </c>
+      <c r="E195" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B196" s="2">
+        <v>10</v>
+      </c>
+      <c r="C196" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D196" s="2">
+        <v>398</v>
+      </c>
+      <c r="E196" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B197" s="2">
+        <v>10</v>
+      </c>
+      <c r="C197" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="D197" s="2">
+        <v>422</v>
+      </c>
+      <c r="E197" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B198" s="2">
+        <v>10</v>
+      </c>
+      <c r="C198" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D198" s="2">
+        <v>470</v>
+      </c>
+      <c r="E198" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B199" s="2">
+        <v>10</v>
+      </c>
+      <c r="C199" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="D199" s="2">
+        <v>521</v>
+      </c>
+      <c r="E199" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B200" s="2">
+        <v>20</v>
+      </c>
+      <c r="C200" s="5">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="D200" s="2">
+        <v>482</v>
+      </c>
+      <c r="E200" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B201" s="2">
+        <v>20</v>
+      </c>
+      <c r="C201" s="5">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="D201" s="2">
+        <v>464</v>
+      </c>
+      <c r="E201" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B202" s="2">
+        <v>20</v>
+      </c>
+      <c r="C202" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D202" s="2">
+        <v>388</v>
+      </c>
+      <c r="E202" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B203" s="2">
+        <v>20</v>
+      </c>
+      <c r="C203" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D203" s="2">
+        <v>370</v>
+      </c>
+      <c r="E203" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B204" s="2">
+        <v>20</v>
+      </c>
+      <c r="C204" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D204" s="2">
+        <v>376</v>
+      </c>
+      <c r="E204" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B205" s="2">
+        <v>20</v>
+      </c>
+      <c r="C205" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D205" s="2">
+        <v>388</v>
+      </c>
+      <c r="E205" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B206" s="2">
+        <v>20</v>
+      </c>
+      <c r="C206" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D206" s="2">
+        <v>415</v>
+      </c>
+      <c r="E206" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B207" s="2">
+        <v>20</v>
+      </c>
+      <c r="C207" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="D207" s="2">
+        <v>444</v>
+      </c>
+      <c r="E207" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B208" s="2">
+        <v>20</v>
+      </c>
+      <c r="C208" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="D208" s="2">
+        <v>468</v>
+      </c>
+      <c r="E208" s="2">
+        <v>315</v>
+      </c>
+      <c r="K208" s="10"/>
+    </row>
+    <row r="209" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B209" s="2">
+        <v>20</v>
+      </c>
+      <c r="C209" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D209" s="2">
+        <v>503</v>
+      </c>
+      <c r="E209" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B210" s="2">
+        <v>20</v>
+      </c>
+      <c r="C210" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="D210" s="2">
+        <v>543</v>
+      </c>
+      <c r="E210" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B211" s="2">
+        <v>30</v>
+      </c>
+      <c r="C211" s="5">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="D211" s="2">
+        <v>437</v>
+      </c>
+      <c r="E211" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B212" s="2">
+        <v>30</v>
+      </c>
+      <c r="C212" s="5">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="D212" s="2">
+        <v>425</v>
+      </c>
+      <c r="E212" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B213" s="2">
+        <v>30</v>
+      </c>
+      <c r="C213" s="5">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="D213" s="2">
+        <v>426</v>
+      </c>
+      <c r="E213" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B214" s="2">
+        <v>30</v>
+      </c>
+      <c r="C214" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="D214" s="2">
+        <v>391</v>
+      </c>
+      <c r="E214" s="2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B215" s="2">
+        <v>30</v>
+      </c>
+      <c r="C215" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D215" s="2">
+        <v>372</v>
+      </c>
+      <c r="E215" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B216" s="2">
+        <v>30</v>
+      </c>
+      <c r="C216" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D216" s="2">
+        <v>372</v>
+      </c>
+      <c r="E216" s="2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B217" s="2">
+        <v>30</v>
+      </c>
+      <c r="C217" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D217" s="2">
+        <v>380</v>
+      </c>
+      <c r="E217" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B218" s="2">
+        <v>30</v>
+      </c>
+      <c r="C218" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D218" s="2">
+        <v>442</v>
+      </c>
+      <c r="E218" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B219" s="2">
+        <v>30</v>
+      </c>
+      <c r="C219" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="D219" s="2">
+        <v>514</v>
+      </c>
+      <c r="E219" s="2">
+        <v>330</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -190,11 +190,20 @@
     <xf borderId="5" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="16" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="16" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -214,19 +223,31 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2470,8 +2491,12 @@
       <c r="E115" s="10">
         <v>435.0</v>
       </c>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
+      <c r="F115" s="17">
+        <v>65.0</v>
+      </c>
+      <c r="G115" s="17">
+        <v>22.3</v>
+      </c>
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
@@ -2508,6 +2533,12 @@
       <c r="E116" s="13">
         <v>407.0</v>
       </c>
+      <c r="F116" s="18">
+        <v>66.0</v>
+      </c>
+      <c r="G116" s="18">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="12">
@@ -2525,6 +2556,12 @@
       <c r="E117" s="13">
         <v>392.0</v>
       </c>
+      <c r="F117" s="18">
+        <v>64.0</v>
+      </c>
+      <c r="G117" s="18">
+        <v>23.3</v>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="12">
@@ -2542,6 +2579,12 @@
       <c r="E118" s="13">
         <v>353.0</v>
       </c>
+      <c r="F118" s="18">
+        <v>64.0</v>
+      </c>
+      <c r="G118" s="18">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="12">
@@ -2559,6 +2602,12 @@
       <c r="E119" s="13">
         <v>338.0</v>
       </c>
+      <c r="F119" s="18">
+        <v>64.0</v>
+      </c>
+      <c r="G119" s="18">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="12">
@@ -2576,22 +2625,34 @@
       <c r="E120" s="13">
         <v>329.0</v>
       </c>
+      <c r="F120" s="18">
+        <v>63.0</v>
+      </c>
+      <c r="G120" s="18">
+        <v>24.0</v>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="12">
         <v>46294.0</v>
       </c>
-      <c r="B121" s="17">
+      <c r="B121" s="19">
         <v>35.0</v>
       </c>
-      <c r="C121" s="18">
+      <c r="C121" s="20">
         <v>0.1</v>
       </c>
-      <c r="D121" s="17">
+      <c r="D121" s="19">
         <v>373.0</v>
       </c>
-      <c r="E121" s="17">
+      <c r="E121" s="19">
         <v>320.0</v>
+      </c>
+      <c r="F121" s="18">
+        <v>63.0</v>
+      </c>
+      <c r="G121" s="18">
+        <v>23.6</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -2610,6 +2671,12 @@
       <c r="E122" s="13">
         <v>306.0</v>
       </c>
+      <c r="F122" s="18">
+        <v>60.0</v>
+      </c>
+      <c r="G122" s="18">
+        <v>24.0</v>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="12">
@@ -2802,16 +2869,16 @@
       <c r="A134" s="12">
         <v>46294.0</v>
       </c>
-      <c r="B134" s="17">
+      <c r="B134" s="19">
         <v>40.0</v>
       </c>
-      <c r="C134" s="18">
+      <c r="C134" s="20">
         <v>0.11</v>
       </c>
-      <c r="D134" s="17">
+      <c r="D134" s="19">
         <v>370.0</v>
       </c>
-      <c r="E134" s="17">
+      <c r="E134" s="19">
         <v>314.0</v>
       </c>
     </row>
@@ -2901,8 +2968,8 @@
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="12">
-        <v>46294.0</v>
+      <c r="A140" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B140" s="13">
         <v>40.0</v>
@@ -2918,8 +2985,8 @@
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="12">
-        <v>46294.0</v>
+      <c r="A141" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B141" s="13">
         <v>40.0</v>
@@ -2935,8 +3002,8 @@
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="12">
-        <v>46294.0</v>
+      <c r="A142" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B142" s="13">
         <v>40.0</v>
@@ -2952,8 +3019,8 @@
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="12">
-        <v>46294.0</v>
+      <c r="A143" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B143" s="13">
         <v>40.0</v>
@@ -2969,8 +3036,8 @@
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="12">
-        <v>46294.0</v>
+      <c r="A144" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B144" s="13">
         <v>40.0</v>
@@ -2986,8 +3053,8 @@
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="12">
-        <v>46294.0</v>
+      <c r="A145" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B145" s="13">
         <v>40.0</v>
@@ -3003,8 +3070,8 @@
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="12">
-        <v>46294.0</v>
+      <c r="A146" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B146" s="13">
         <v>40.0</v>
@@ -3020,8 +3087,8 @@
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="12">
-        <v>46294.0</v>
+      <c r="A147" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B147" s="13">
         <v>40.0</v>
@@ -3037,8 +3104,8 @@
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="12">
-        <v>46294.0</v>
+      <c r="A148" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B148" s="13">
         <v>40.0</v>
@@ -3054,8 +3121,8 @@
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="12">
-        <v>46294.0</v>
+      <c r="A149" s="21">
+        <v>46302.0</v>
       </c>
       <c r="B149" s="13">
         <v>40.0</v>
@@ -3071,138 +3138,138 @@
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="19">
+      <c r="A150" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B150" s="20">
+      <c r="B150" s="23">
         <v>45.0</v>
       </c>
-      <c r="C150" s="21">
+      <c r="C150" s="24">
         <v>0.047</v>
       </c>
-      <c r="D150" s="20">
+      <c r="D150" s="23">
         <v>557.0</v>
       </c>
-      <c r="E150" s="20">
+      <c r="E150" s="23">
         <v>423.0</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="19">
+      <c r="A151" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B151" s="20">
+      <c r="B151" s="23">
         <v>45.0</v>
       </c>
-      <c r="C151" s="21">
+      <c r="C151" s="24">
         <v>0.052</v>
       </c>
-      <c r="D151" s="20">
+      <c r="D151" s="23">
         <v>495.0</v>
       </c>
-      <c r="E151" s="20">
+      <c r="E151" s="23">
         <v>378.0</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="19">
+      <c r="A152" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B152" s="20">
+      <c r="B152" s="23">
         <v>45.0</v>
       </c>
-      <c r="C152" s="21">
+      <c r="C152" s="24">
         <v>0.06</v>
       </c>
-      <c r="D152" s="20">
+      <c r="D152" s="23">
         <v>460.0</v>
       </c>
-      <c r="E152" s="20">
+      <c r="E152" s="23">
         <v>351.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="19">
+      <c r="A153" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B153" s="17">
+      <c r="B153" s="19">
         <v>45.0</v>
       </c>
-      <c r="C153" s="18">
+      <c r="C153" s="20">
         <v>0.07</v>
       </c>
-      <c r="D153" s="17">
+      <c r="D153" s="19">
         <v>424.0</v>
       </c>
-      <c r="E153" s="17">
+      <c r="E153" s="19">
         <v>338.0</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="19">
+      <c r="A154" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B154" s="20">
+      <c r="B154" s="23">
         <v>45.0</v>
       </c>
-      <c r="C154" s="21">
+      <c r="C154" s="24">
         <v>0.078</v>
       </c>
-      <c r="D154" s="20">
+      <c r="D154" s="23">
         <v>435.0</v>
       </c>
-      <c r="E154" s="20">
+      <c r="E154" s="23">
         <v>331.0</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="19">
+      <c r="A155" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B155" s="20">
+      <c r="B155" s="23">
         <v>45.0</v>
       </c>
-      <c r="C155" s="21">
+      <c r="C155" s="24">
         <v>0.087</v>
       </c>
-      <c r="D155" s="20">
+      <c r="D155" s="23">
         <v>451.0</v>
       </c>
-      <c r="E155" s="20">
+      <c r="E155" s="23">
         <v>327.0</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="19">
+      <c r="A156" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B156" s="20">
+      <c r="B156" s="23">
         <v>45.0</v>
       </c>
-      <c r="C156" s="21">
+      <c r="C156" s="24">
         <v>0.1</v>
       </c>
-      <c r="D156" s="20">
+      <c r="D156" s="23">
         <v>408.0</v>
       </c>
-      <c r="E156" s="20">
+      <c r="E156" s="23">
         <v>319.0</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="19">
+      <c r="A157" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B157" s="20">
+      <c r="B157" s="23">
         <v>45.0</v>
       </c>
-      <c r="C157" s="21">
+      <c r="C157" s="24">
         <v>0.18</v>
       </c>
-      <c r="D157" s="20">
+      <c r="D157" s="23">
         <v>462.0</v>
       </c>
-      <c r="E157" s="20">
+      <c r="E157" s="23">
         <v>307.0</v>
       </c>
     </row>
@@ -3278,16 +3345,16 @@
       <c r="A162" s="12">
         <v>46294.0</v>
       </c>
-      <c r="B162" s="17">
+      <c r="B162" s="19">
         <v>25.0</v>
       </c>
-      <c r="C162" s="18">
+      <c r="C162" s="20">
         <v>0.17</v>
       </c>
-      <c r="D162" s="17">
+      <c r="D162" s="19">
         <v>363.0</v>
       </c>
-      <c r="E162" s="17">
+      <c r="E162" s="19">
         <v>308.0</v>
       </c>
     </row>
@@ -3394,70 +3461,70 @@
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="19">
+      <c r="A169" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B169" s="20">
+      <c r="B169" s="23">
         <v>15.0</v>
       </c>
-      <c r="C169" s="21">
+      <c r="C169" s="24">
         <v>0.11</v>
       </c>
-      <c r="D169" s="20">
+      <c r="D169" s="23">
         <v>516.0</v>
       </c>
-      <c r="E169" s="20">
+      <c r="E169" s="23">
         <v>421.0</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="19">
+      <c r="A170" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B170" s="20">
+      <c r="B170" s="23">
         <v>15.0</v>
       </c>
-      <c r="C170" s="21">
+      <c r="C170" s="24">
         <v>0.15</v>
       </c>
-      <c r="D170" s="20">
+      <c r="D170" s="23">
         <v>403.0</v>
       </c>
-      <c r="E170" s="20">
+      <c r="E170" s="23">
         <v>348.0</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="19">
+      <c r="A171" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B171" s="20">
+      <c r="B171" s="23">
         <v>15.0</v>
       </c>
-      <c r="C171" s="21">
+      <c r="C171" s="24">
         <v>0.19</v>
       </c>
-      <c r="D171" s="20">
+      <c r="D171" s="23">
         <v>367.0</v>
       </c>
-      <c r="E171" s="20">
+      <c r="E171" s="23">
         <v>321.0</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="19">
+      <c r="A172" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B172" s="20">
+      <c r="B172" s="23">
         <v>15.0</v>
       </c>
-      <c r="C172" s="21">
+      <c r="C172" s="24">
         <v>0.23</v>
       </c>
-      <c r="D172" s="20">
+      <c r="D172" s="23">
         <v>358.0</v>
       </c>
-      <c r="E172" s="20">
+      <c r="E172" s="23">
         <v>311.0</v>
       </c>
     </row>
@@ -3465,118 +3532,118 @@
       <c r="A173" s="12">
         <v>46294.0</v>
       </c>
-      <c r="B173" s="17">
+      <c r="B173" s="19">
         <v>15.0</v>
       </c>
-      <c r="C173" s="18">
+      <c r="C173" s="20">
         <v>0.27</v>
       </c>
-      <c r="D173" s="17">
+      <c r="D173" s="19">
         <v>348.0</v>
       </c>
-      <c r="E173" s="17">
+      <c r="E173" s="19">
         <v>305.0</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="19">
+      <c r="A174" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B174" s="20">
+      <c r="B174" s="23">
         <v>15.0</v>
       </c>
-      <c r="C174" s="21">
+      <c r="C174" s="24">
         <v>0.32</v>
       </c>
-      <c r="D174" s="20">
+      <c r="D174" s="23">
         <v>358.0</v>
       </c>
-      <c r="E174" s="20">
+      <c r="E174" s="23">
         <v>302.0</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="19">
+      <c r="A175" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B175" s="20">
+      <c r="B175" s="23">
         <v>15.0</v>
       </c>
-      <c r="C175" s="21">
+      <c r="C175" s="24">
         <v>0.42</v>
       </c>
-      <c r="D175" s="20">
+      <c r="D175" s="23">
         <v>369.0</v>
       </c>
-      <c r="E175" s="20">
+      <c r="E175" s="23">
         <v>303.0</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="19">
+      <c r="A176" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B176" s="20">
+      <c r="B176" s="23">
         <v>15.0</v>
       </c>
-      <c r="C176" s="21">
+      <c r="C176" s="24">
         <v>0.53</v>
       </c>
-      <c r="D176" s="20">
+      <c r="D176" s="23">
         <v>403.0</v>
       </c>
-      <c r="E176" s="20">
+      <c r="E176" s="23">
         <v>305.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="19">
+      <c r="A177" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B177" s="20">
+      <c r="B177" s="23">
         <v>15.0</v>
       </c>
-      <c r="C177" s="21">
+      <c r="C177" s="24">
         <v>0.64</v>
       </c>
-      <c r="D177" s="20">
+      <c r="D177" s="23">
         <v>438.0</v>
       </c>
-      <c r="E177" s="20">
+      <c r="E177" s="23">
         <v>309.0</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="19">
+      <c r="A178" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B178" s="20">
+      <c r="B178" s="23">
         <v>15.0</v>
       </c>
-      <c r="C178" s="21">
+      <c r="C178" s="24">
         <v>0.7</v>
       </c>
-      <c r="D178" s="20">
+      <c r="D178" s="23">
         <v>465.0</v>
       </c>
-      <c r="E178" s="20">
+      <c r="E178" s="23">
         <v>314.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="19">
+      <c r="A179" s="22">
         <v>46294.0</v>
       </c>
-      <c r="B179" s="22">
+      <c r="B179" s="25">
         <v>15.0</v>
       </c>
-      <c r="C179" s="23">
+      <c r="C179" s="26">
         <v>0.8</v>
       </c>
-      <c r="D179" s="22">
+      <c r="D179" s="25">
         <v>501.0</v>
       </c>
-      <c r="E179" s="22">
+      <c r="E179" s="25">
         <v>317.0</v>
       </c>
     </row>
@@ -3596,8 +3663,12 @@
       <c r="E180" s="10">
         <v>373.0</v>
       </c>
-      <c r="F180" s="7"/>
-      <c r="G180" s="7"/>
+      <c r="F180" s="17">
+        <v>63.0</v>
+      </c>
+      <c r="G180" s="17">
+        <v>23.6</v>
+      </c>
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
       <c r="J180" s="7"/>
@@ -3634,6 +3705,12 @@
       <c r="E181" s="13">
         <v>332.0</v>
       </c>
+      <c r="F181" s="18">
+        <v>62.0</v>
+      </c>
+      <c r="G181" s="17">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3">
@@ -3651,6 +3728,12 @@
       <c r="E182" s="13">
         <v>320.0</v>
       </c>
+      <c r="F182" s="18">
+        <v>61.0</v>
+      </c>
+      <c r="G182" s="18">
+        <v>23.0</v>
+      </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3">
@@ -3668,6 +3751,12 @@
       <c r="E183" s="13">
         <v>306.0</v>
       </c>
+      <c r="F183" s="18">
+        <v>59.0</v>
+      </c>
+      <c r="G183" s="17">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3">
@@ -3690,16 +3779,16 @@
       <c r="A185" s="3">
         <v>46295.0</v>
       </c>
-      <c r="B185" s="17">
+      <c r="B185" s="19">
         <v>5.0</v>
       </c>
-      <c r="C185" s="18">
+      <c r="C185" s="20">
         <v>0.72</v>
       </c>
-      <c r="D185" s="17">
+      <c r="D185" s="19">
         <v>339.0</v>
       </c>
-      <c r="E185" s="17">
+      <c r="E185" s="19">
         <v>298.0</v>
       </c>
     </row>
@@ -3772,172 +3861,172 @@
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="24">
+      <c r="A190" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B190" s="20">
+      <c r="B190" s="23">
         <v>10.0</v>
       </c>
-      <c r="C190" s="21">
+      <c r="C190" s="24">
         <v>0.18</v>
       </c>
-      <c r="D190" s="20">
+      <c r="D190" s="23">
         <v>476.0</v>
       </c>
-      <c r="E190" s="20">
+      <c r="E190" s="23">
         <v>396.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="24">
+      <c r="A191" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B191" s="20">
+      <c r="B191" s="23">
         <v>10.0</v>
       </c>
-      <c r="C191" s="21">
+      <c r="C191" s="24">
         <v>0.24</v>
       </c>
-      <c r="D191" s="20">
+      <c r="D191" s="23">
         <v>394.0</v>
       </c>
-      <c r="E191" s="20">
+      <c r="E191" s="23">
         <v>340.0</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="24">
+      <c r="A192" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B192" s="20">
+      <c r="B192" s="23">
         <v>10.0</v>
       </c>
-      <c r="C192" s="21">
+      <c r="C192" s="24">
         <v>0.32</v>
       </c>
-      <c r="D192" s="20">
+      <c r="D192" s="23">
         <v>356.0</v>
       </c>
-      <c r="E192" s="20">
+      <c r="E192" s="23">
         <v>310.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="25">
+      <c r="A193" s="28">
         <v>46295.0</v>
       </c>
-      <c r="B193" s="17">
+      <c r="B193" s="19">
         <v>10.0</v>
       </c>
-      <c r="C193" s="18">
+      <c r="C193" s="20">
         <v>0.42</v>
       </c>
-      <c r="D193" s="17">
+      <c r="D193" s="19">
         <v>354.0</v>
       </c>
-      <c r="E193" s="17">
+      <c r="E193" s="19">
         <v>304.0</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="24">
+      <c r="A194" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B194" s="20">
+      <c r="B194" s="23">
         <v>10.0</v>
       </c>
-      <c r="C194" s="21">
+      <c r="C194" s="24">
         <v>0.48</v>
       </c>
-      <c r="D194" s="20">
+      <c r="D194" s="23">
         <v>355.0</v>
       </c>
-      <c r="E194" s="20">
+      <c r="E194" s="23">
         <v>307.0</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="24">
+      <c r="A195" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B195" s="20">
+      <c r="B195" s="23">
         <v>10.0</v>
       </c>
-      <c r="C195" s="21">
+      <c r="C195" s="24">
         <v>0.6</v>
       </c>
-      <c r="D195" s="20">
+      <c r="D195" s="23">
         <v>371.0</v>
       </c>
-      <c r="E195" s="20">
+      <c r="E195" s="23">
         <v>308.0</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="24">
+      <c r="A196" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B196" s="20">
+      <c r="B196" s="23">
         <v>10.0</v>
       </c>
-      <c r="C196" s="21">
+      <c r="C196" s="24">
         <v>0.7</v>
       </c>
-      <c r="D196" s="20">
+      <c r="D196" s="23">
         <v>398.0</v>
       </c>
-      <c r="E196" s="20">
+      <c r="E196" s="23">
         <v>308.0</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="24">
+      <c r="A197" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B197" s="20">
+      <c r="B197" s="23">
         <v>10.0</v>
       </c>
-      <c r="C197" s="21">
+      <c r="C197" s="24">
         <v>0.79</v>
       </c>
-      <c r="D197" s="20">
+      <c r="D197" s="23">
         <v>422.0</v>
       </c>
-      <c r="E197" s="20">
+      <c r="E197" s="23">
         <v>309.0</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="24">
+      <c r="A198" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B198" s="20">
+      <c r="B198" s="23">
         <v>10.0</v>
       </c>
-      <c r="C198" s="21">
+      <c r="C198" s="24">
         <v>0.9</v>
       </c>
-      <c r="D198" s="20">
+      <c r="D198" s="23">
         <v>470.0</v>
       </c>
-      <c r="E198" s="20">
+      <c r="E198" s="23">
         <v>313.0</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="24">
+      <c r="A199" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B199" s="20">
+      <c r="B199" s="23">
         <v>10.0</v>
       </c>
-      <c r="C199" s="21">
+      <c r="C199" s="24">
         <v>0.99</v>
       </c>
-      <c r="D199" s="20">
+      <c r="D199" s="23">
         <v>521.0</v>
       </c>
-      <c r="E199" s="20">
+      <c r="E199" s="23">
         <v>318.0</v>
       </c>
     </row>
@@ -3993,19 +4082,19 @@
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="25">
+      <c r="A203" s="28">
         <v>46295.0</v>
       </c>
-      <c r="B203" s="17">
+      <c r="B203" s="19">
         <v>20.0</v>
       </c>
-      <c r="C203" s="18">
+      <c r="C203" s="20">
         <v>0.17</v>
       </c>
-      <c r="D203" s="17">
+      <c r="D203" s="19">
         <v>370.0</v>
       </c>
-      <c r="E203" s="17">
+      <c r="E203" s="19">
         <v>316.0</v>
       </c>
     </row>
@@ -4130,178 +4219,178 @@
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="24">
+      <c r="A211" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B211" s="20">
+      <c r="B211" s="23">
         <v>30.0</v>
       </c>
-      <c r="C211" s="21">
+      <c r="C211" s="24">
         <v>0.069</v>
       </c>
-      <c r="D211" s="20">
+      <c r="D211" s="23">
         <v>437.0</v>
       </c>
-      <c r="E211" s="20">
+      <c r="E211" s="23">
         <v>374.0</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="24">
+      <c r="A212" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B212" s="20">
+      <c r="B212" s="23">
         <v>30.0</v>
       </c>
-      <c r="C212" s="21">
+      <c r="C212" s="24">
         <v>0.074</v>
       </c>
-      <c r="D212" s="20">
+      <c r="D212" s="23">
         <v>425.0</v>
       </c>
-      <c r="E212" s="20">
+      <c r="E212" s="23">
         <v>364.0</v>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="24">
+      <c r="A213" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B213" s="20">
+      <c r="B213" s="23">
         <v>30.0</v>
       </c>
-      <c r="C213" s="21">
+      <c r="C213" s="24">
         <v>0.083</v>
       </c>
-      <c r="D213" s="20">
+      <c r="D213" s="23">
         <v>426.0</v>
       </c>
-      <c r="E213" s="20">
+      <c r="E213" s="23">
         <v>346.0</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="24">
+      <c r="A214" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B214" s="20">
+      <c r="B214" s="23">
         <v>30.0</v>
       </c>
-      <c r="C214" s="21">
+      <c r="C214" s="24">
         <v>0.09</v>
       </c>
-      <c r="D214" s="20">
+      <c r="D214" s="23">
         <v>391.0</v>
       </c>
-      <c r="E214" s="20">
+      <c r="E214" s="23">
         <v>339.0</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="25">
+      <c r="A215" s="28">
         <v>46295.0</v>
       </c>
-      <c r="B215" s="17">
+      <c r="B215" s="19">
         <v>30.0</v>
       </c>
-      <c r="C215" s="18">
+      <c r="C215" s="20">
         <v>0.1</v>
       </c>
-      <c r="D215" s="17">
+      <c r="D215" s="19">
         <v>372.0</v>
       </c>
-      <c r="E215" s="17">
+      <c r="E215" s="19">
         <v>326.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="24">
+      <c r="A216" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B216" s="20">
+      <c r="B216" s="23">
         <v>30.0</v>
       </c>
-      <c r="C216" s="21">
+      <c r="C216" s="24">
         <v>0.14</v>
       </c>
-      <c r="D216" s="20">
+      <c r="D216" s="23">
         <v>372.0</v>
       </c>
-      <c r="E216" s="20">
+      <c r="E216" s="23">
         <v>315.0</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="24">
+      <c r="A217" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B217" s="20">
+      <c r="B217" s="23">
         <v>30.0</v>
       </c>
-      <c r="C217" s="21">
+      <c r="C217" s="24">
         <v>0.22</v>
       </c>
-      <c r="D217" s="20">
+      <c r="D217" s="23">
         <v>380.0</v>
       </c>
-      <c r="E217" s="20">
+      <c r="E217" s="23">
         <v>300.0</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="24">
+      <c r="A218" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B218" s="20">
+      <c r="B218" s="23">
         <v>30.0</v>
       </c>
-      <c r="C218" s="21">
+      <c r="C218" s="24">
         <v>0.32</v>
       </c>
-      <c r="D218" s="20">
+      <c r="D218" s="23">
         <v>442.0</v>
       </c>
-      <c r="E218" s="20">
+      <c r="E218" s="23">
         <v>309.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="24">
+      <c r="A219" s="27">
         <v>46295.0</v>
       </c>
-      <c r="B219" s="22">
+      <c r="B219" s="25">
         <v>30.0</v>
       </c>
-      <c r="C219" s="23">
+      <c r="C219" s="26">
         <v>0.44</v>
       </c>
-      <c r="D219" s="22">
+      <c r="D219" s="25">
         <v>514.0</v>
       </c>
-      <c r="E219" s="22">
+      <c r="E219" s="25">
         <v>330.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="26">
+      <c r="A220" s="29">
         <v>46301.0</v>
       </c>
-      <c r="B220" s="27">
+      <c r="B220" s="17">
         <v>30.0</v>
       </c>
-      <c r="C220" s="28">
+      <c r="C220" s="30">
         <v>0.056</v>
       </c>
-      <c r="D220" s="27">
+      <c r="D220" s="17">
         <v>563.0</v>
       </c>
-      <c r="E220" s="27">
+      <c r="E220" s="17">
         <v>437.0</v>
       </c>
-      <c r="F220" s="27">
+      <c r="F220" s="17">
         <v>57.0</v>
       </c>
-      <c r="G220" s="27">
+      <c r="G220" s="17">
         <v>23.6</v>
       </c>
       <c r="H220" s="7"/>
@@ -4325,450 +4414,820 @@
       <c r="Z220" s="7"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="29">
+      <c r="A221" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B221" s="30">
+      <c r="B221" s="18">
         <v>30.0</v>
       </c>
-      <c r="C221" s="31">
+      <c r="C221" s="32">
         <v>0.061</v>
       </c>
-      <c r="D221" s="30">
+      <c r="D221" s="18">
         <v>507.0</v>
       </c>
-      <c r="E221" s="30">
+      <c r="E221" s="18">
         <v>403.0</v>
       </c>
-      <c r="F221" s="30">
+      <c r="F221" s="18">
         <v>57.0</v>
       </c>
-      <c r="G221" s="30">
+      <c r="G221" s="18">
         <v>24.3</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="29">
+      <c r="A222" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B222" s="30">
+      <c r="B222" s="18">
         <v>30.0</v>
       </c>
-      <c r="C222" s="31">
+      <c r="C222" s="32">
         <v>0.071</v>
       </c>
-      <c r="D222" s="30">
+      <c r="D222" s="18">
         <v>438.0</v>
       </c>
-      <c r="E222" s="30">
+      <c r="E222" s="18">
         <v>367.0</v>
       </c>
+      <c r="F222" s="18">
+        <v>59.0</v>
+      </c>
+      <c r="G222" s="18">
+        <v>23.3</v>
+      </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="29">
+      <c r="A223" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B223" s="30">
+      <c r="B223" s="18">
         <v>30.0</v>
       </c>
-      <c r="C223" s="31">
+      <c r="C223" s="32">
         <v>0.082</v>
       </c>
-      <c r="D223" s="30">
+      <c r="D223" s="18">
         <v>411.0</v>
       </c>
-      <c r="E223" s="30">
+      <c r="E223" s="18">
         <v>349.0</v>
       </c>
+      <c r="F223" s="18">
+        <v>58.0</v>
+      </c>
+      <c r="G223" s="18">
+        <v>24.0</v>
+      </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="29">
+      <c r="A224" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B224" s="30">
+      <c r="B224" s="18">
         <v>30.0</v>
       </c>
-      <c r="C224" s="31">
+      <c r="C224" s="32">
         <v>0.094</v>
       </c>
-      <c r="D224" s="30">
+      <c r="D224" s="18">
         <v>401.0</v>
       </c>
-      <c r="E224" s="30">
+      <c r="E224" s="18">
         <v>334.0</v>
       </c>
+      <c r="F224" s="18">
+        <v>57.0</v>
+      </c>
+      <c r="G224" s="18">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="29">
+      <c r="A225" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B225" s="30">
+      <c r="B225" s="18">
         <v>30.0</v>
       </c>
-      <c r="C225" s="31">
+      <c r="C225" s="32">
         <v>0.1</v>
       </c>
-      <c r="D225" s="30">
+      <c r="D225" s="18">
         <v>385.0</v>
       </c>
-      <c r="E225" s="30">
+      <c r="E225" s="18">
         <v>327.0</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="29">
+      <c r="A226" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B226" s="30">
+      <c r="B226" s="18">
         <v>30.0</v>
       </c>
-      <c r="C226" s="31">
+      <c r="C226" s="32">
         <v>0.15</v>
       </c>
-      <c r="D226" s="30">
+      <c r="D226" s="18">
         <v>368.0</v>
       </c>
-      <c r="E226" s="30">
+      <c r="E226" s="18">
         <v>310.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="29">
+      <c r="A227" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B227" s="30">
+      <c r="B227" s="18">
         <v>30.0</v>
       </c>
-      <c r="C227" s="31">
+      <c r="C227" s="32">
         <v>0.2</v>
       </c>
-      <c r="D227" s="30">
+      <c r="D227" s="18">
         <v>383.0</v>
       </c>
-      <c r="E227" s="30">
+      <c r="E227" s="18">
         <v>306.0</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="29">
+      <c r="A228" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B228" s="30">
+      <c r="B228" s="18">
         <v>30.0</v>
       </c>
-      <c r="C228" s="31">
+      <c r="C228" s="32">
         <v>0.26</v>
       </c>
-      <c r="D228" s="30">
+      <c r="D228" s="18">
         <v>403.0</v>
       </c>
-      <c r="E228" s="30">
+      <c r="E228" s="18">
         <v>304.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="29">
+      <c r="A229" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B229" s="30">
+      <c r="B229" s="18">
         <v>30.0</v>
       </c>
-      <c r="C229" s="31">
+      <c r="C229" s="32">
         <v>0.35</v>
       </c>
-      <c r="D229" s="30">
+      <c r="D229" s="18">
         <v>446.0</v>
       </c>
-      <c r="E229" s="30">
+      <c r="E229" s="18">
         <v>310.0</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="29">
+      <c r="A230" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B230" s="30">
+      <c r="B230" s="18">
         <v>30.0</v>
       </c>
-      <c r="C230" s="31">
+      <c r="C230" s="32">
         <v>0.44</v>
       </c>
-      <c r="D230" s="30">
+      <c r="D230" s="18">
         <v>494.0</v>
       </c>
-      <c r="E230" s="30">
+      <c r="E230" s="18">
         <v>320.0</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="29">
+      <c r="A231" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B231" s="30">
+      <c r="B231" s="18">
         <v>30.0</v>
       </c>
-      <c r="C231" s="31">
+      <c r="C231" s="32">
         <v>0.54</v>
       </c>
-      <c r="D231" s="30">
+      <c r="D231" s="18">
         <v>555.0</v>
       </c>
-      <c r="E231" s="30">
+      <c r="E231" s="18">
         <v>325.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="29">
+      <c r="A232" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B232" s="30">
+      <c r="B232" s="34">
         <v>35.0</v>
       </c>
-      <c r="C232" s="31">
+      <c r="C232" s="35">
         <v>0.052</v>
       </c>
-      <c r="D232" s="30">
+      <c r="D232" s="34">
         <v>550.0</v>
       </c>
-      <c r="E232" s="30">
+      <c r="E232" s="34">
         <v>421.0</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="29">
+      <c r="A233" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B233" s="30">
+      <c r="B233" s="34">
         <v>35.0</v>
       </c>
-      <c r="C233" s="31">
+      <c r="C233" s="35">
         <v>0.056</v>
       </c>
-      <c r="D233" s="30">
+      <c r="D233" s="34">
         <v>496.0</v>
       </c>
-      <c r="E233" s="30">
+      <c r="E233" s="34">
         <v>392.0</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="29">
+      <c r="A234" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B234" s="30">
+      <c r="B234" s="34">
         <v>35.0</v>
       </c>
-      <c r="C234" s="31">
+      <c r="C234" s="35">
         <v>0.064</v>
       </c>
-      <c r="D234" s="30">
+      <c r="D234" s="34">
         <v>447.0</v>
       </c>
-      <c r="E234" s="30">
+      <c r="E234" s="34">
         <v>368.0</v>
       </c>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="29">
+      <c r="A235" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B235" s="30">
+      <c r="B235" s="34">
         <v>35.0</v>
       </c>
-      <c r="C235" s="31">
+      <c r="C235" s="35">
         <v>0.075</v>
       </c>
-      <c r="D235" s="30">
+      <c r="D235" s="34">
         <v>411.0</v>
       </c>
-      <c r="E235" s="30">
+      <c r="E235" s="34">
         <v>346.0</v>
       </c>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="29">
+      <c r="A236" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B236" s="30">
+      <c r="B236" s="34">
         <v>35.0</v>
       </c>
-      <c r="C236" s="31">
+      <c r="C236" s="35">
         <v>0.083</v>
       </c>
-      <c r="D236" s="30">
+      <c r="D236" s="34">
         <v>396.0</v>
       </c>
-      <c r="E236" s="30">
+      <c r="E236" s="34">
         <v>337.0</v>
       </c>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="29">
+      <c r="A237" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B237" s="30">
+      <c r="B237" s="34">
         <v>35.0</v>
       </c>
-      <c r="C237" s="31">
+      <c r="C237" s="35">
         <v>0.092</v>
       </c>
-      <c r="D237" s="30">
+      <c r="D237" s="34">
         <v>401.0</v>
       </c>
-      <c r="E237" s="30">
+      <c r="E237" s="34">
         <v>330.0</v>
       </c>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="29">
+      <c r="A238" s="36">
         <v>46301.0</v>
       </c>
-      <c r="B238" s="30">
+      <c r="B238" s="37">
         <v>35.0</v>
       </c>
-      <c r="C238" s="31">
+      <c r="C238" s="38">
         <v>0.12</v>
       </c>
-      <c r="D238" s="30">
+      <c r="D238" s="37">
         <v>394.0</v>
       </c>
-      <c r="E238" s="30">
+      <c r="E238" s="37">
         <v>316.0</v>
       </c>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="29">
+      <c r="A239" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B239" s="30">
+      <c r="B239" s="34">
         <v>35.0</v>
       </c>
-      <c r="C239" s="31">
+      <c r="C239" s="35">
         <v>0.16</v>
       </c>
-      <c r="D239" s="30">
+      <c r="D239" s="34">
         <v>384.0</v>
       </c>
-      <c r="E239" s="30">
+      <c r="E239" s="34">
         <v>309.0</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="29">
+      <c r="A240" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B240" s="30">
+      <c r="B240" s="34">
         <v>35.0</v>
       </c>
-      <c r="C240" s="31">
+      <c r="C240" s="35">
         <v>0.21</v>
       </c>
-      <c r="D240" s="30">
+      <c r="D240" s="34">
         <v>401.0</v>
       </c>
-      <c r="E240" s="30">
+      <c r="E240" s="34">
         <v>306.0</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="29">
+      <c r="A241" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B241" s="30">
+      <c r="B241" s="34">
         <v>35.0</v>
       </c>
-      <c r="C241" s="31">
+      <c r="C241" s="35">
         <v>0.28</v>
       </c>
-      <c r="D241" s="30">
+      <c r="D241" s="34">
         <v>444.0</v>
       </c>
-      <c r="E241" s="30">
+      <c r="E241" s="34">
         <v>308.0</v>
       </c>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="29">
+      <c r="A242" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B242" s="30">
+      <c r="B242" s="34">
         <v>35.0</v>
       </c>
+      <c r="C242" s="35">
+        <v>0.39</v>
+      </c>
+      <c r="D242" s="34">
+        <v>518.0</v>
+      </c>
+      <c r="E242" s="34">
+        <v>321.0</v>
+      </c>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="29">
+      <c r="A243" s="33">
         <v>46301.0</v>
       </c>
-      <c r="B243" s="30">
+      <c r="B243" s="34">
         <v>35.0</v>
       </c>
+      <c r="C243" s="35">
+        <v>0.43</v>
+      </c>
+      <c r="D243" s="34">
+        <v>541.0</v>
+      </c>
+      <c r="E243" s="34">
+        <v>323.0</v>
+      </c>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="29">
+      <c r="A244" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B244" s="30">
-        <v>35.0</v>
+      <c r="B244" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C244" s="32">
+        <v>0.045</v>
+      </c>
+      <c r="D244" s="18">
+        <v>548.0</v>
+      </c>
+      <c r="E244" s="18">
+        <v>426.0</v>
       </c>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="29">
+      <c r="A245" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B245" s="30">
-        <v>35.0</v>
+      <c r="B245" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C245" s="32">
+        <v>0.053</v>
+      </c>
+      <c r="D245" s="18">
+        <v>457.0</v>
+      </c>
+      <c r="E245" s="18">
+        <v>381.0</v>
       </c>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="29">
+      <c r="A246" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B246" s="30">
-        <v>35.0</v>
+      <c r="B246" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C246" s="32">
+        <v>0.062</v>
+      </c>
+      <c r="D246" s="18">
+        <v>427.0</v>
+      </c>
+      <c r="E246" s="18">
+        <v>358.0</v>
       </c>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="29">
+      <c r="A247" s="31">
         <v>46301.0</v>
       </c>
-      <c r="B247" s="30">
-        <v>35.0</v>
+      <c r="B247" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C247" s="32">
+        <v>0.068</v>
+      </c>
+      <c r="D247" s="18">
+        <v>421.0</v>
+      </c>
+      <c r="E247" s="18">
+        <v>347.0</v>
       </c>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="29">
+      <c r="A248" s="31">
         <v>46301.0</v>
       </c>
+      <c r="B248" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C248" s="32">
+        <v>0.078</v>
+      </c>
+      <c r="D248" s="18">
+        <v>402.0</v>
+      </c>
+      <c r="E248" s="18">
+        <v>337.0</v>
+      </c>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="29">
+      <c r="A249" s="31">
         <v>46301.0</v>
       </c>
+      <c r="B249" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C249" s="32">
+        <v>0.086</v>
+      </c>
+      <c r="D249" s="18">
+        <v>417.0</v>
+      </c>
+      <c r="E249" s="18">
+        <v>332.0</v>
+      </c>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="29">
+      <c r="A250" s="31">
         <v>46301.0</v>
       </c>
-    </row>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
+      <c r="B250" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C250" s="32">
+        <v>0.093</v>
+      </c>
+      <c r="D250" s="18">
+        <v>384.0</v>
+      </c>
+      <c r="E250" s="18">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="A251" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B251" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C251" s="32">
+        <v>0.11</v>
+      </c>
+      <c r="D251" s="18">
+        <v>384.0</v>
+      </c>
+      <c r="E251" s="18">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="A252" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B252" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C252" s="32">
+        <v>0.19</v>
+      </c>
+      <c r="D252" s="18">
+        <v>419.0</v>
+      </c>
+      <c r="E252" s="18">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="A253" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B253" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C253" s="32">
+        <v>0.25</v>
+      </c>
+      <c r="D253" s="18">
+        <v>462.0</v>
+      </c>
+      <c r="E253" s="18">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="A254" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B254" s="18">
+        <v>40.0</v>
+      </c>
+      <c r="C254" s="32">
+        <v>0.36</v>
+      </c>
+      <c r="D254" s="18">
+        <v>534.0</v>
+      </c>
+      <c r="E254" s="18">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B255" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C255" s="32">
+        <v>0.16</v>
+      </c>
+      <c r="D255" s="18">
+        <v>532.0</v>
+      </c>
+      <c r="E255" s="18">
+        <v>433.0</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="A256" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B256" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C256" s="32">
+        <v>0.23</v>
+      </c>
+      <c r="D256" s="18">
+        <v>399.0</v>
+      </c>
+      <c r="E256" s="18">
+        <v>345.0</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B257" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C257" s="32">
+        <v>0.28</v>
+      </c>
+      <c r="D257" s="18">
+        <v>372.0</v>
+      </c>
+      <c r="E257" s="18">
+        <v>324.0</v>
+      </c>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="A258" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B258" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C258" s="32">
+        <v>0.32</v>
+      </c>
+      <c r="D258" s="18">
+        <v>353.0</v>
+      </c>
+      <c r="E258" s="18">
+        <v>311.0</v>
+      </c>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="A259" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B259" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C259" s="32">
+        <v>0.35</v>
+      </c>
+      <c r="D259" s="18">
+        <v>350.0</v>
+      </c>
+      <c r="E259" s="18">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="A260" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B260" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C260" s="32">
+        <v>0.42</v>
+      </c>
+      <c r="D260" s="18">
+        <v>351.0</v>
+      </c>
+      <c r="E260" s="18">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="A261" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B261" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C261" s="32">
+        <v>0.47</v>
+      </c>
+      <c r="D261" s="18">
+        <v>363.0</v>
+      </c>
+      <c r="E261" s="18">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="A262" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B262" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C262" s="32">
+        <v>0.56</v>
+      </c>
+      <c r="D262" s="18">
+        <v>369.0</v>
+      </c>
+      <c r="E262" s="18">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="A263" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B263" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C263" s="32">
+        <v>0.65</v>
+      </c>
+      <c r="D263" s="18">
+        <v>384.0</v>
+      </c>
+      <c r="E263" s="18">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="A264" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B264" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C264" s="32">
+        <v>0.74</v>
+      </c>
+      <c r="D264" s="18">
+        <v>418.0</v>
+      </c>
+      <c r="E264" s="18">
+        <v>312.0</v>
+      </c>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="A265" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B265" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C265" s="32">
+        <v>0.83</v>
+      </c>
+      <c r="D265" s="18">
+        <v>442.0</v>
+      </c>
+      <c r="E265" s="18">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="A266" s="31">
+        <v>46301.0</v>
+      </c>
+      <c r="B266" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C266" s="32">
+        <v>0.93</v>
+      </c>
+      <c r="D266" s="18">
+        <v>482.0</v>
+      </c>
+      <c r="E266" s="18">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="A267" s="31"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="A268" s="31"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="A269" s="31"/>
+    </row>
     <row r="270" ht="15.75" customHeight="1"/>
     <row r="271" ht="15.75" customHeight="1"/>
     <row r="272" ht="15.75" customHeight="1"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,21 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brio\Documents\Ley_de_Paschen\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEB4734-EA33-4EA1-AB7A-855C55CE4B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="+HZbGVJqjjHP6FmRYHuoZrb9uV+t2n2MWgGA4K0nFaw="/>
@@ -51,42 +42,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -96,7 +81,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -111,31 +96,17 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -150,7 +121,6 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -165,7 +135,23 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="medium">
@@ -178,91 +164,87 @@
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="35">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="16" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="16" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="6" fillId="3" fontId="4" numFmtId="16" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf borderId="7" fillId="3" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="16" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="16" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="11" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="11" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="11" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -452,22 +434,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="26" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="10.71"/>
+    <col customWidth="1" min="6" max="6" width="11.86"/>
+    <col customWidth="1" min="7" max="26" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,652 +491,652 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C2" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="D2" s="3">
-        <v>455</v>
+        <v>455.0</v>
       </c>
       <c r="E2" s="3">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>381.0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C3" s="3">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="D3" s="3">
-        <v>426</v>
+        <v>426.0</v>
       </c>
       <c r="E3" s="3">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>362.0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B4" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="D4" s="3">
-        <v>433</v>
+        <v>433.0</v>
       </c>
       <c r="E4" s="3">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>349.0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B5" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C5" s="3">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="D5" s="3">
-        <v>417</v>
+        <v>417.0</v>
       </c>
       <c r="E5" s="3">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>339.0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C6" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="D6" s="3">
-        <v>392</v>
+        <v>392.0</v>
       </c>
       <c r="E6" s="3">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>331.0</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B7" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C7" s="3">
         <v>0.1</v>
       </c>
       <c r="D7" s="3">
-        <v>376</v>
+        <v>376.0</v>
       </c>
       <c r="E7" s="3">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B8" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C8" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D8" s="3">
-        <v>386</v>
+        <v>386.0</v>
       </c>
       <c r="E8" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B9" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C9" s="3">
         <v>0.18</v>
       </c>
       <c r="D9" s="3">
-        <v>395</v>
+        <v>395.0</v>
       </c>
       <c r="E9" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B10" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C10" s="3">
         <v>0.23</v>
       </c>
       <c r="D10" s="3">
-        <v>430</v>
+        <v>430.0</v>
       </c>
       <c r="E10" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B11" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C11" s="3">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="D11" s="3">
-        <v>460</v>
+        <v>460.0</v>
       </c>
       <c r="E11" s="3">
-        <v>308</v>
+        <v>308.0</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B12" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C12" s="3">
         <v>0.34</v>
       </c>
       <c r="D12" s="3">
-        <v>493</v>
+        <v>493.0</v>
       </c>
       <c r="E12" s="3">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B13" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C13" s="3">
         <v>0.38</v>
       </c>
       <c r="D13" s="3">
-        <v>528</v>
+        <v>528.0</v>
       </c>
       <c r="E13" s="3">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B14" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C14" s="3">
         <v>0.43</v>
       </c>
       <c r="D14" s="3">
-        <v>561</v>
+        <v>561.0</v>
       </c>
       <c r="E14" s="3">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B15" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C15" s="3">
         <v>0.48</v>
       </c>
       <c r="D15" s="3">
-        <v>585</v>
+        <v>585.0</v>
       </c>
       <c r="E15" s="3">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B16" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C16" s="3">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="D16" s="3">
-        <v>495</v>
+        <v>495.0</v>
       </c>
       <c r="E16" s="3">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>379.0</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B17" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C17" s="3">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="D17" s="3">
-        <v>445</v>
+        <v>445.0</v>
       </c>
       <c r="E17" s="3">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B18" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C18" s="3">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="D18" s="3">
-        <v>435</v>
+        <v>435.0</v>
       </c>
       <c r="E18" s="3">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>352.0</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B19" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C19" s="3">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="D19" s="3">
-        <v>451</v>
+        <v>451.0</v>
       </c>
       <c r="E19" s="3">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>344.0</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B20" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C20" s="3">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="D20" s="3">
-        <v>378</v>
+        <v>378.0</v>
       </c>
       <c r="E20" s="3">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>355.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B21" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C21" s="3">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="D21" s="3">
-        <v>396</v>
+        <v>396.0</v>
       </c>
       <c r="E21" s="3">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B22" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C22" s="3">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="D22" s="3">
-        <v>412</v>
+        <v>412.0</v>
       </c>
       <c r="E22" s="3">
-        <v>344</v>
+        <v>344.0</v>
       </c>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B23" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C23" s="3">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="D23" s="3">
-        <v>409</v>
+        <v>409.0</v>
       </c>
       <c r="E23" s="3">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>342.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B24" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C24" s="3">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="D24" s="3">
-        <v>397</v>
+        <v>397.0</v>
       </c>
       <c r="E24" s="3">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>338.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B25" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C25" s="3">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="D25" s="3">
-        <v>459</v>
+        <v>459.0</v>
       </c>
       <c r="E25" s="3">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B26" s="3">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C26" s="3">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="D26" s="3">
-        <v>436</v>
+        <v>436.0</v>
       </c>
       <c r="E26" s="3">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>332.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B27" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C27" s="3">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="D27" s="3">
-        <v>612</v>
+        <v>612.0</v>
       </c>
       <c r="E27" s="3">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>480.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B28" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C28" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D28" s="3">
-        <v>431</v>
+        <v>431.0</v>
       </c>
       <c r="E28" s="3">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>370.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B29" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C29" s="3">
         <v>0.2</v>
       </c>
       <c r="D29" s="3">
-        <v>388</v>
+        <v>388.0</v>
       </c>
       <c r="E29" s="3">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B30" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C30" s="3">
         <v>0.27</v>
       </c>
       <c r="D30" s="3">
-        <v>362</v>
+        <v>362.0</v>
       </c>
       <c r="E30" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B31" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C31" s="3">
         <v>0.31</v>
       </c>
       <c r="D31" s="3">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="E31" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B32" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C32" s="3">
         <v>0.33</v>
       </c>
       <c r="D32" s="3">
-        <v>362</v>
+        <v>362.0</v>
       </c>
       <c r="E32" s="3">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B33" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C33" s="3">
         <v>0.4</v>
       </c>
       <c r="D33" s="3">
-        <v>375</v>
+        <v>375.0</v>
       </c>
       <c r="E33" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B34" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C34" s="3">
         <v>0.45</v>
       </c>
       <c r="D34" s="3">
-        <v>398</v>
+        <v>398.0</v>
       </c>
       <c r="E34" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B35" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C35" s="3">
         <v>0.48</v>
       </c>
       <c r="D35" s="3">
-        <v>398</v>
+        <v>398.0</v>
       </c>
       <c r="E35" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B36" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C36" s="3">
         <v>0.61</v>
       </c>
       <c r="D36" s="3">
-        <v>431</v>
+        <v>431.0</v>
       </c>
       <c r="E36" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B37" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C37" s="3">
         <v>0.72</v>
       </c>
       <c r="D37" s="3">
-        <v>472</v>
+        <v>472.0</v>
       </c>
       <c r="E37" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2">
-        <v>46261</v>
+        <v>46261.0</v>
       </c>
       <c r="B38" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C38" s="3">
         <v>0.81</v>
       </c>
       <c r="D38" s="3">
-        <v>508</v>
+        <v>508.0</v>
       </c>
       <c r="E38" s="3">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="5">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B39" s="6">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C39" s="6">
         <v>0.18</v>
       </c>
       <c r="D39" s="6">
-        <v>515</v>
+        <v>515.0</v>
       </c>
       <c r="E39" s="6">
-        <v>418</v>
+        <v>418.0</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -1178,820 +1160,820 @@
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B40" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C40" s="3">
         <v>0.22</v>
       </c>
       <c r="D40" s="3">
-        <v>448</v>
+        <v>448.0</v>
       </c>
       <c r="E40" s="3">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B41" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C41" s="3">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="D41" s="3">
-        <v>381</v>
+        <v>381.0</v>
       </c>
       <c r="E41" s="3">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B42" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C42" s="3">
         <v>0.34</v>
       </c>
       <c r="D42" s="3">
-        <v>366</v>
+        <v>366.0</v>
       </c>
       <c r="E42" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B43" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C43" s="3">
         <v>0.37</v>
       </c>
       <c r="D43" s="3">
-        <v>364</v>
+        <v>364.0</v>
       </c>
       <c r="E43" s="3">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B44" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C44" s="3">
         <v>0.4</v>
       </c>
       <c r="D44" s="3">
-        <v>356</v>
+        <v>356.0</v>
       </c>
       <c r="E44" s="3">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B45" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C45" s="3">
         <v>0.44</v>
       </c>
       <c r="D45" s="3">
-        <v>364</v>
+        <v>364.0</v>
       </c>
       <c r="E45" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B46" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C46" s="3">
         <v>0.51</v>
       </c>
       <c r="D46" s="3">
-        <v>356</v>
+        <v>356.0</v>
       </c>
       <c r="E46" s="3">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B47" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C47" s="3">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="D47" s="3">
-        <v>369</v>
+        <v>369.0</v>
       </c>
       <c r="E47" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B48" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C48" s="3">
         <v>0.6</v>
       </c>
       <c r="D48" s="3">
-        <v>364</v>
+        <v>364.0</v>
       </c>
       <c r="E48" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B49" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C49" s="3">
         <v>0.63</v>
       </c>
       <c r="D49" s="3">
-        <v>380</v>
+        <v>380.0</v>
       </c>
       <c r="E49" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B50" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C50" s="3">
         <v>0.68</v>
       </c>
       <c r="D50" s="3">
-        <v>390</v>
+        <v>390.0</v>
       </c>
       <c r="E50" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B51" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C51" s="3">
         <v>0.75</v>
       </c>
       <c r="D51" s="3">
-        <v>414</v>
+        <v>414.0</v>
       </c>
       <c r="E51" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B52" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C52" s="3">
         <v>0.85</v>
       </c>
       <c r="D52" s="3">
-        <v>422</v>
+        <v>422.0</v>
       </c>
       <c r="E52" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B53" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C53" s="3">
         <v>0.95</v>
       </c>
       <c r="D53" s="3">
-        <v>469</v>
+        <v>469.0</v>
       </c>
       <c r="E53" s="3">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B54" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C54" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="D54" s="3">
-        <v>497</v>
+        <v>497.0</v>
       </c>
       <c r="E54" s="3">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B55" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C55" s="3">
         <v>0.84</v>
       </c>
       <c r="D55" s="3">
-        <v>438</v>
+        <v>438.0</v>
       </c>
       <c r="E55" s="3">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B56" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C56" s="3">
         <v>0.19</v>
       </c>
       <c r="D56" s="3">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E56" s="3">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B57" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C57" s="3">
         <v>0.1</v>
       </c>
       <c r="D57" s="3">
-        <v>585</v>
+        <v>585.0</v>
       </c>
       <c r="E57" s="3">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>458.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B58" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C58" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D58" s="3">
-        <v>429</v>
+        <v>429.0</v>
       </c>
       <c r="E58" s="3">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B59" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C59" s="3">
         <v>0.18</v>
       </c>
       <c r="D59" s="3">
-        <v>389</v>
+        <v>389.0</v>
       </c>
       <c r="E59" s="3">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329.0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B60" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C60" s="3">
         <v>0.22</v>
       </c>
       <c r="D60" s="3">
-        <v>364</v>
+        <v>364.0</v>
       </c>
       <c r="E60" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B61" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C61" s="3">
         <v>0.26</v>
       </c>
       <c r="D61" s="3">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="E61" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B62" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C62" s="3">
         <v>0.34</v>
       </c>
       <c r="D62" s="3">
-        <v>366</v>
+        <v>366.0</v>
       </c>
       <c r="E62" s="3">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B63" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C63" s="3">
         <v>0.41</v>
       </c>
       <c r="D63" s="3">
-        <v>373</v>
+        <v>373.0</v>
       </c>
       <c r="E63" s="3">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B64" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C64" s="3">
         <v>0.46</v>
       </c>
       <c r="D64" s="3">
-        <v>386</v>
+        <v>386.0</v>
       </c>
       <c r="E64" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B65" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C65" s="3">
         <v>0.53</v>
       </c>
       <c r="D65" s="3">
-        <v>404</v>
+        <v>404.0</v>
       </c>
       <c r="E65" s="3">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B66" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C66" s="3">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="D66" s="3">
-        <v>426</v>
+        <v>426.0</v>
       </c>
       <c r="E66" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B67" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C67" s="3">
         <v>0.64</v>
       </c>
       <c r="D67" s="3">
-        <v>437</v>
+        <v>437.0</v>
       </c>
       <c r="E67" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B68" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C68" s="3">
         <v>0.73</v>
       </c>
       <c r="D68" s="3">
-        <v>471</v>
+        <v>471.0</v>
       </c>
       <c r="E68" s="3">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B69" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C69" s="3">
         <v>0.79</v>
       </c>
       <c r="D69" s="3">
-        <v>496</v>
+        <v>496.0</v>
       </c>
       <c r="E69" s="3">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B70" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C70" s="3">
         <v>0.85</v>
       </c>
       <c r="D70" s="3">
-        <v>521</v>
+        <v>521.0</v>
       </c>
       <c r="E70" s="3">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329.0</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B71" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C71" s="3">
         <v>0.9</v>
       </c>
       <c r="D71" s="3">
-        <v>547</v>
+        <v>547.0</v>
       </c>
       <c r="E71" s="3">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330.0</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B72" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C72" s="3">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="D72" s="3">
-        <v>516</v>
+        <v>516.0</v>
       </c>
       <c r="E72" s="3">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>427.0</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B73" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C73" s="3">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="D73" s="3">
-        <v>491</v>
+        <v>491.0</v>
       </c>
       <c r="E73" s="3">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>410.0</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B74" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C74" s="3">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="D74" s="3">
-        <v>466</v>
+        <v>466.0</v>
       </c>
       <c r="E74" s="3">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>395.0</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B75" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C75" s="3">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="D75" s="3">
-        <v>442</v>
+        <v>442.0</v>
       </c>
       <c r="E75" s="3">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>381.0</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B76" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C76" s="3">
         <v>0.12</v>
       </c>
       <c r="D76" s="3">
-        <v>395</v>
+        <v>395.0</v>
       </c>
       <c r="E76" s="3">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346.0</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B77" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C77" s="3">
         <v>0.15</v>
       </c>
       <c r="D77" s="3">
-        <v>382</v>
+        <v>382.0</v>
       </c>
       <c r="E77" s="3">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B78" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C78" s="3">
         <v>0.21</v>
       </c>
       <c r="D78" s="3">
-        <v>356</v>
+        <v>356.0</v>
       </c>
       <c r="E78" s="3">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311.0</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B79" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C79" s="3">
         <v>0.32</v>
       </c>
       <c r="D79" s="3">
-        <v>374</v>
+        <v>374.0</v>
       </c>
       <c r="E79" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B80" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C80" s="3">
         <v>0.38</v>
       </c>
       <c r="D80" s="3">
-        <v>396</v>
+        <v>396.0</v>
       </c>
       <c r="E80" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B81" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C81" s="3">
         <v>0.44</v>
       </c>
       <c r="D81" s="3">
-        <v>422</v>
+        <v>422.0</v>
       </c>
       <c r="E81" s="3">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B82" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C82" s="3">
         <v>0.54</v>
       </c>
       <c r="D82" s="3">
-        <v>466</v>
+        <v>466.0</v>
       </c>
       <c r="E82" s="3">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B83" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C83" s="3">
         <v>0.62</v>
       </c>
       <c r="D83" s="3">
-        <v>497</v>
+        <v>497.0</v>
       </c>
       <c r="E83" s="3">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B84" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C84" s="3">
         <v>0.68</v>
       </c>
       <c r="D84" s="3">
-        <v>522</v>
+        <v>522.0</v>
       </c>
       <c r="E84" s="3">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329.0</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B85" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C85" s="3">
         <v>0.72</v>
       </c>
       <c r="D85" s="3">
-        <v>530</v>
+        <v>530.0</v>
       </c>
       <c r="E85" s="3">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329.0</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="7">
-        <v>46262</v>
+        <v>46262.0</v>
       </c>
       <c r="B86" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C86" s="3">
         <v>0.79</v>
       </c>
       <c r="D86" s="3">
-        <v>578</v>
+        <v>578.0</v>
       </c>
       <c r="E86" s="3">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>333.0</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B87" s="9">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C87" s="10">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="D87" s="9">
-        <v>469</v>
+        <v>469.0</v>
       </c>
       <c r="E87" s="9">
-        <v>376</v>
+        <v>376.0</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
@@ -2015,483 +1997,483 @@
       <c r="Y87" s="6"/>
       <c r="Z87" s="6"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B88" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C88" s="13">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="D88" s="12">
-        <v>435</v>
+        <v>435.0</v>
       </c>
       <c r="E88" s="12">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>363.0</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B89" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C89" s="13">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="D89" s="12">
-        <v>418</v>
+        <v>418.0</v>
       </c>
       <c r="E89" s="12">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>345.0</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B90" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C90" s="13">
         <v>0.13</v>
       </c>
       <c r="D90" s="12">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E90" s="12">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319.0</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B91" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C91" s="13">
         <v>0.17</v>
       </c>
       <c r="D91" s="12">
-        <v>367</v>
+        <v>367.0</v>
       </c>
       <c r="E91" s="12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B92" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C92" s="13">
         <v>0.19</v>
       </c>
       <c r="D92" s="12">
-        <v>374</v>
+        <v>374.0</v>
       </c>
       <c r="E92" s="12">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B93" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C93" s="13">
         <v>0.24</v>
       </c>
       <c r="D93" s="12">
-        <v>382</v>
+        <v>382.0</v>
       </c>
       <c r="E93" s="12">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B94" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C94" s="13">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="D94" s="12">
-        <v>401</v>
+        <v>401.0</v>
       </c>
       <c r="E94" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B95" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C95" s="13">
         <v>0.33</v>
       </c>
       <c r="D95" s="12">
-        <v>410</v>
+        <v>410.0</v>
       </c>
       <c r="E95" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B96" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C96" s="13">
         <v>0.37</v>
       </c>
       <c r="D96" s="12">
-        <v>427</v>
+        <v>427.0</v>
       </c>
       <c r="E96" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B97" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C97" s="13">
         <v>0.44</v>
       </c>
       <c r="D97" s="12">
-        <v>467</v>
+        <v>467.0</v>
       </c>
       <c r="E97" s="12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B98" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C98" s="13">
         <v>0.5</v>
       </c>
       <c r="D98" s="12">
-        <v>490</v>
+        <v>490.0</v>
       </c>
       <c r="E98" s="12">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324.0</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B99" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C99" s="13">
         <v>0.53</v>
       </c>
       <c r="D99" s="12">
-        <v>508</v>
+        <v>508.0</v>
       </c>
       <c r="E99" s="12">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B100" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C100" s="13">
         <v>0.6</v>
       </c>
       <c r="D100" s="12">
-        <v>541</v>
+        <v>541.0</v>
       </c>
       <c r="E100" s="12">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B101" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C101" s="13">
         <v>0.68</v>
       </c>
       <c r="D101" s="12">
-        <v>574</v>
+        <v>574.0</v>
       </c>
       <c r="E101" s="12">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>322.0</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B102" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C102" s="13">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="D102" s="12">
-        <v>455</v>
+        <v>455.0</v>
       </c>
       <c r="E102" s="12">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>399.0</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B103" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C103" s="13">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="D103" s="12">
-        <v>426</v>
+        <v>426.0</v>
       </c>
       <c r="E103" s="12">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>366.0</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B104" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C104" s="13">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="D104" s="12">
-        <v>394</v>
+        <v>394.0</v>
       </c>
       <c r="E104" s="12">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346.0</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B105" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C105" s="13">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="D105" s="12">
-        <v>385</v>
+        <v>385.0</v>
       </c>
       <c r="E105" s="12">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>333.0</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B106" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C106" s="13">
         <v>0.1</v>
       </c>
       <c r="D106" s="12">
-        <v>379</v>
+        <v>379.0</v>
       </c>
       <c r="E106" s="12">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B107" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C107" s="13">
         <v>0.13</v>
       </c>
       <c r="D107" s="12">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="E107" s="12">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>313.0</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B108" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C108" s="13">
         <v>0.17</v>
       </c>
       <c r="D108" s="12">
-        <v>368</v>
+        <v>368.0</v>
       </c>
       <c r="E108" s="12">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B109" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C109" s="13">
         <v>0.2</v>
       </c>
       <c r="D109" s="12">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E109" s="12">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B110" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C110" s="13">
         <v>0.26</v>
       </c>
       <c r="D110" s="12">
-        <v>419</v>
+        <v>419.0</v>
       </c>
       <c r="E110" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B111" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C111" s="13">
         <v>0.35</v>
       </c>
       <c r="D111" s="12">
-        <v>462</v>
+        <v>462.0</v>
       </c>
       <c r="E111" s="12">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B112" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C112" s="13">
         <v>0.44</v>
       </c>
       <c r="D112" s="12">
-        <v>506</v>
+        <v>506.0</v>
       </c>
       <c r="E112" s="12">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B113" s="12">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C113" s="13">
         <v>0.51</v>
       </c>
       <c r="D113" s="12">
-        <v>532</v>
+        <v>532.0</v>
       </c>
       <c r="E113" s="12">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324.0</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="11">
-        <v>46288</v>
+        <v>46288.0</v>
       </c>
       <c r="B114" s="14">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C114" s="15">
-        <v>0.56000000000000005</v>
+        <v>0.56</v>
       </c>
       <c r="D114" s="14">
-        <v>570</v>
+        <v>570.0</v>
       </c>
       <c r="E114" s="14">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>322.0</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="8">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B115" s="9">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C115" s="10">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="D115" s="9">
-        <v>557</v>
+        <v>557.0</v>
       </c>
       <c r="E115" s="9">
-        <v>435</v>
+        <v>435.0</v>
       </c>
       <c r="F115" s="6">
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="G115" s="6">
         <v>22.3</v>
@@ -2516,1154 +2498,1154 @@
       <c r="Y115" s="6"/>
       <c r="Z115" s="6"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B116" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C116" s="13">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="D116" s="12">
-        <v>531</v>
+        <v>531.0</v>
       </c>
       <c r="E116" s="12">
-        <v>407</v>
+        <v>407.0</v>
       </c>
       <c r="F116" s="3">
-        <v>66</v>
+        <v>66.0</v>
       </c>
       <c r="G116" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B117" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C117" s="13">
-        <v>5.8000000000000003E-2</v>
+        <v>0.058</v>
       </c>
       <c r="D117" s="12">
-        <v>496</v>
+        <v>496.0</v>
       </c>
       <c r="E117" s="12">
-        <v>392</v>
+        <v>392.0</v>
       </c>
       <c r="F117" s="3">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="G117" s="3">
         <v>23.3</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B118" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C118" s="13">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="D118" s="12">
-        <v>434</v>
+        <v>434.0</v>
       </c>
       <c r="E118" s="12">
-        <v>353</v>
+        <v>353.0</v>
       </c>
       <c r="F118" s="3">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="G118" s="3">
         <v>23.6</v>
       </c>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B119" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C119" s="13">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="D119" s="12">
-        <v>409</v>
+        <v>409.0</v>
       </c>
       <c r="E119" s="12">
-        <v>338</v>
+        <v>338.0</v>
       </c>
       <c r="F119" s="3">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="G119" s="3">
         <v>23.6</v>
       </c>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B120" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C120" s="13">
         <v>0.09</v>
       </c>
       <c r="D120" s="12">
-        <v>379</v>
+        <v>379.0</v>
       </c>
       <c r="E120" s="12">
-        <v>329</v>
+        <v>329.0</v>
       </c>
       <c r="F120" s="3">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G120" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B121" s="16">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C121" s="17">
         <v>0.1</v>
       </c>
       <c r="D121" s="16">
-        <v>373</v>
+        <v>373.0</v>
       </c>
       <c r="E121" s="16">
-        <v>320</v>
+        <v>320.0</v>
       </c>
       <c r="F121" s="3">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G121" s="3">
         <v>23.6</v>
       </c>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B122" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C122" s="13">
         <v>0.16</v>
       </c>
       <c r="D122" s="12">
-        <v>374</v>
+        <v>374.0</v>
       </c>
       <c r="E122" s="12">
-        <v>306</v>
+        <v>306.0</v>
       </c>
       <c r="F122" s="3">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="G122" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B123" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C123" s="13">
         <v>0.22</v>
       </c>
       <c r="D123" s="12">
-        <v>411</v>
+        <v>411.0</v>
       </c>
       <c r="E123" s="12">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B124" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C124" s="13">
         <v>0.27</v>
       </c>
       <c r="D124" s="12">
-        <v>447</v>
+        <v>447.0</v>
       </c>
       <c r="E124" s="12">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B125" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C125" s="13">
         <v>0.33</v>
       </c>
       <c r="D125" s="12">
-        <v>477</v>
+        <v>477.0</v>
       </c>
       <c r="E125" s="12">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B126" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C126" s="13">
         <v>0.4</v>
       </c>
       <c r="D126" s="12">
-        <v>531</v>
+        <v>531.0</v>
       </c>
       <c r="E126" s="12">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B127" s="12">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C127" s="13">
         <v>0.47</v>
       </c>
       <c r="D127" s="12">
-        <v>566</v>
+        <v>566.0</v>
       </c>
       <c r="E127" s="12">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B128" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C128" s="13">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="D128" s="12">
-        <v>451</v>
+        <v>451.0</v>
       </c>
       <c r="E128" s="12">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>385.0</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B129" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C129" s="13">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="D129" s="12">
-        <v>454</v>
+        <v>454.0</v>
       </c>
       <c r="E129" s="12">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>366.0</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B130" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C130" s="13">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="D130" s="12">
-        <v>437</v>
+        <v>437.0</v>
       </c>
       <c r="E130" s="12">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>349.0</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B131" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C131" s="13">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="D131" s="12">
-        <v>406</v>
+        <v>406.0</v>
       </c>
       <c r="E131" s="12">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335.0</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B132" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C132" s="13">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="D132" s="12">
-        <v>420</v>
+        <v>420.0</v>
       </c>
       <c r="E132" s="12">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B133" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C133" s="13">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="D133" s="12">
-        <v>396</v>
+        <v>396.0</v>
       </c>
       <c r="E133" s="12">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B134" s="16">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C134" s="17">
         <v>0.11</v>
       </c>
       <c r="D134" s="16">
-        <v>370</v>
+        <v>370.0</v>
       </c>
       <c r="E134" s="16">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B135" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C135" s="13">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D135" s="12">
-        <v>393</v>
+        <v>393.0</v>
       </c>
       <c r="E135" s="12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B136" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C136" s="13">
         <v>0.2</v>
       </c>
       <c r="D136" s="12">
-        <v>440</v>
+        <v>440.0</v>
       </c>
       <c r="E136" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B137" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C137" s="13">
         <v>0.25</v>
       </c>
       <c r="D137" s="12">
-        <v>453</v>
+        <v>453.0</v>
       </c>
       <c r="E137" s="12">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B138" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C138" s="13">
         <v>0.31</v>
       </c>
       <c r="D138" s="12">
-        <v>489</v>
+        <v>489.0</v>
       </c>
       <c r="E138" s="12">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319.0</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B139" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C139" s="13">
         <v>0.37</v>
       </c>
       <c r="D139" s="12">
-        <v>550</v>
+        <v>550.0</v>
       </c>
       <c r="E139" s="12">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319.0</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B140" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C140" s="13">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="D140" s="12">
-        <v>542</v>
+        <v>542.0</v>
       </c>
       <c r="E140" s="12">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>419.0</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B141" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C141" s="13">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="D141" s="12">
-        <v>461</v>
+        <v>461.0</v>
       </c>
       <c r="E141" s="12">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376.0</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B142" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C142" s="13">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="D142" s="12">
-        <v>420</v>
+        <v>420.0</v>
       </c>
       <c r="E142" s="12">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>353.0</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B143" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C143" s="13">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="D143" s="12">
-        <v>410</v>
+        <v>410.0</v>
       </c>
       <c r="E143" s="12">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337.0</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B144" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C144" s="13">
         <v>0.08</v>
       </c>
       <c r="D144" s="12">
-        <v>410</v>
+        <v>410.0</v>
       </c>
       <c r="E144" s="12">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330.0</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B145" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C145" s="13">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="D145" s="12">
-        <v>402</v>
+        <v>402.0</v>
       </c>
       <c r="E145" s="12">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B146" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C146" s="13">
         <v>0.1</v>
       </c>
       <c r="D146" s="12">
-        <v>401</v>
+        <v>401.0</v>
       </c>
       <c r="E146" s="12">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B147" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C147" s="13">
         <v>0.17</v>
       </c>
       <c r="D147" s="12">
-        <v>409</v>
+        <v>409.0</v>
       </c>
       <c r="E147" s="12">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B148" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C148" s="13">
         <v>0.24</v>
       </c>
       <c r="D148" s="12">
-        <v>451</v>
+        <v>451.0</v>
       </c>
       <c r="E148" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="11">
-        <v>46293</v>
+        <v>46293.0</v>
       </c>
       <c r="B149" s="12">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C149" s="13">
         <v>0.34</v>
       </c>
       <c r="D149" s="12">
-        <v>532</v>
+        <v>532.0</v>
       </c>
       <c r="E149" s="12">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B150" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C150" s="20">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="D150" s="19">
-        <v>557</v>
+        <v>557.0</v>
       </c>
       <c r="E150" s="19">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>423.0</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B151" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C151" s="20">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="D151" s="19">
-        <v>495</v>
+        <v>495.0</v>
       </c>
       <c r="E151" s="19">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378.0</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B152" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C152" s="20">
         <v>0.06</v>
       </c>
       <c r="D152" s="19">
-        <v>460</v>
+        <v>460.0</v>
       </c>
       <c r="E152" s="19">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>351.0</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B153" s="16">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C153" s="17">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="D153" s="16">
-        <v>424</v>
+        <v>424.0</v>
       </c>
       <c r="E153" s="16">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>338.0</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B154" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C154" s="20">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="D154" s="19">
-        <v>435</v>
+        <v>435.0</v>
       </c>
       <c r="E154" s="19">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331.0</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B155" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C155" s="20">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="D155" s="19">
-        <v>451</v>
+        <v>451.0</v>
       </c>
       <c r="E155" s="19">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B156" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C156" s="20">
         <v>0.1</v>
       </c>
       <c r="D156" s="19">
-        <v>408</v>
+        <v>408.0</v>
       </c>
       <c r="E156" s="19">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319.0</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B157" s="19">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C157" s="20">
         <v>0.18</v>
       </c>
       <c r="D157" s="19">
-        <v>462</v>
+        <v>462.0</v>
       </c>
       <c r="E157" s="19">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B158" s="12">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="C158" s="13">
         <v>0.27</v>
       </c>
       <c r="D158" s="12">
-        <v>503</v>
+        <v>503.0</v>
       </c>
       <c r="E158" s="12">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319.0</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B159" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C159" s="13">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="D159" s="12">
-        <v>436</v>
+        <v>436.0</v>
       </c>
       <c r="E159" s="12">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>375.0</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B160" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C160" s="13">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="D160" s="12">
-        <v>426</v>
+        <v>426.0</v>
       </c>
       <c r="E160" s="12">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>353.0</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B161" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C161" s="13">
         <v>0.1</v>
       </c>
       <c r="D161" s="12">
-        <v>398</v>
+        <v>398.0</v>
       </c>
       <c r="E161" s="12">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>338.0</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B162" s="16">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C162" s="17">
         <v>0.17</v>
       </c>
       <c r="D162" s="16">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="E162" s="16">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B163" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C163" s="13">
         <v>0.23</v>
       </c>
       <c r="D163" s="12">
-        <v>373</v>
+        <v>373.0</v>
       </c>
       <c r="E163" s="12">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B164" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C164" s="13">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="D164" s="12">
-        <v>399</v>
+        <v>399.0</v>
       </c>
       <c r="E164" s="12">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302.0</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B165" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C165" s="13">
         <v>0.39</v>
       </c>
       <c r="D165" s="12">
-        <v>450</v>
+        <v>450.0</v>
       </c>
       <c r="E165" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B166" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C166" s="13">
         <v>0.45</v>
       </c>
       <c r="D166" s="12">
-        <v>478</v>
+        <v>478.0</v>
       </c>
       <c r="E166" s="12">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B167" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C167" s="13">
         <v>0.51</v>
       </c>
       <c r="D167" s="12">
-        <v>510</v>
+        <v>510.0</v>
       </c>
       <c r="E167" s="12">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B168" s="12">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C168" s="13">
         <v>0.61</v>
       </c>
       <c r="D168" s="12">
-        <v>558</v>
+        <v>558.0</v>
       </c>
       <c r="E168" s="12">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B169" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C169" s="20">
         <v>0.11</v>
       </c>
       <c r="D169" s="19">
-        <v>516</v>
+        <v>516.0</v>
       </c>
       <c r="E169" s="19">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>421.0</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B170" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C170" s="20">
         <v>0.15</v>
       </c>
       <c r="D170" s="19">
-        <v>403</v>
+        <v>403.0</v>
       </c>
       <c r="E170" s="19">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348.0</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B171" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C171" s="20">
         <v>0.19</v>
       </c>
       <c r="D171" s="19">
-        <v>367</v>
+        <v>367.0</v>
       </c>
       <c r="E171" s="19">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B172" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C172" s="20">
         <v>0.23</v>
       </c>
       <c r="D172" s="19">
-        <v>358</v>
+        <v>358.0</v>
       </c>
       <c r="E172" s="19">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311.0</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="11">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B173" s="16">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C173" s="17">
         <v>0.27</v>
       </c>
       <c r="D173" s="16">
-        <v>348</v>
+        <v>348.0</v>
       </c>
       <c r="E173" s="16">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B174" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C174" s="20">
         <v>0.32</v>
       </c>
       <c r="D174" s="19">
-        <v>358</v>
+        <v>358.0</v>
       </c>
       <c r="E174" s="19">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302.0</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B175" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C175" s="20">
         <v>0.42</v>
       </c>
       <c r="D175" s="19">
-        <v>369</v>
+        <v>369.0</v>
       </c>
       <c r="E175" s="19">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B176" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C176" s="20">
         <v>0.53</v>
       </c>
       <c r="D176" s="19">
-        <v>403</v>
+        <v>403.0</v>
       </c>
       <c r="E176" s="19">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B177" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C177" s="20">
         <v>0.64</v>
       </c>
       <c r="D177" s="19">
-        <v>438</v>
+        <v>438.0</v>
       </c>
       <c r="E177" s="19">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B178" s="19">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C178" s="20">
         <v>0.7</v>
       </c>
       <c r="D178" s="19">
-        <v>465</v>
+        <v>465.0</v>
       </c>
       <c r="E178" s="19">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="18">
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="B179" s="21">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="C179" s="22">
         <v>0.8</v>
       </c>
       <c r="D179" s="21">
-        <v>501</v>
+        <v>501.0</v>
       </c>
       <c r="E179" s="21">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>317.0</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="5">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B180" s="9">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C180" s="10">
         <v>0.42</v>
       </c>
       <c r="D180" s="9">
-        <v>443</v>
+        <v>443.0</v>
       </c>
       <c r="E180" s="9">
-        <v>373</v>
+        <v>373.0</v>
       </c>
       <c r="F180" s="6">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G180" s="6">
         <v>23.6</v>
@@ -3688,706 +3670,706 @@
       <c r="Y180" s="6"/>
       <c r="Z180" s="6"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B181" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C181" s="13">
         <v>0.5</v>
       </c>
       <c r="D181" s="12">
-        <v>380</v>
+        <v>380.0</v>
       </c>
       <c r="E181" s="12">
-        <v>332</v>
+        <v>332.0</v>
       </c>
       <c r="F181" s="3">
-        <v>62</v>
+        <v>62.0</v>
       </c>
       <c r="G181" s="6">
         <v>23.6</v>
       </c>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B182" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C182" s="13">
         <v>0.54</v>
       </c>
       <c r="D182" s="12">
-        <v>369</v>
+        <v>369.0</v>
       </c>
       <c r="E182" s="12">
-        <v>320</v>
+        <v>320.0</v>
       </c>
       <c r="F182" s="3">
-        <v>61</v>
+        <v>61.0</v>
       </c>
       <c r="G182" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B183" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C183" s="13">
         <v>0.63</v>
       </c>
       <c r="D183" s="12">
-        <v>358</v>
+        <v>358.0</v>
       </c>
       <c r="E183" s="12">
-        <v>306</v>
+        <v>306.0</v>
       </c>
       <c r="F183" s="3">
-        <v>59</v>
+        <v>59.0</v>
       </c>
       <c r="G183" s="6">
         <v>23.6</v>
       </c>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B184" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C184" s="13">
         <v>0.67</v>
       </c>
       <c r="D184" s="12">
-        <v>346</v>
+        <v>346.0</v>
       </c>
       <c r="E184" s="12">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B185" s="16">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C185" s="17">
         <v>0.72</v>
       </c>
       <c r="D185" s="16">
-        <v>339</v>
+        <v>339.0</v>
       </c>
       <c r="E185" s="16">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298.0</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B186" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C186" s="13">
         <v>0.77</v>
       </c>
       <c r="D186" s="12">
-        <v>354</v>
+        <v>354.0</v>
       </c>
       <c r="E186" s="12">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>297.0</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B187" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C187" s="13">
         <v>0.86</v>
       </c>
       <c r="D187" s="12">
-        <v>353</v>
+        <v>353.0</v>
       </c>
       <c r="E187" s="12">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>297.0</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B188" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C188" s="13">
         <v>0.9</v>
       </c>
       <c r="D188" s="12">
-        <v>361</v>
+        <v>361.0</v>
       </c>
       <c r="E188" s="12">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299.0</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B189" s="12">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="C189" s="13">
         <v>0.99</v>
       </c>
       <c r="D189" s="12">
-        <v>380</v>
+        <v>380.0</v>
       </c>
       <c r="E189" s="12">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>399.0</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B190" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C190" s="20">
         <v>0.18</v>
       </c>
       <c r="D190" s="19">
-        <v>476</v>
+        <v>476.0</v>
       </c>
       <c r="E190" s="19">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>396.0</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B191" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C191" s="20">
         <v>0.24</v>
       </c>
       <c r="D191" s="19">
-        <v>394</v>
+        <v>394.0</v>
       </c>
       <c r="E191" s="19">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>340.0</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B192" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C192" s="20">
         <v>0.32</v>
       </c>
       <c r="D192" s="19">
-        <v>356</v>
+        <v>356.0</v>
       </c>
       <c r="E192" s="19">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="24">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B193" s="16">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C193" s="17">
         <v>0.42</v>
       </c>
       <c r="D193" s="16">
-        <v>354</v>
+        <v>354.0</v>
       </c>
       <c r="E193" s="16">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B194" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C194" s="20">
         <v>0.48</v>
       </c>
       <c r="D194" s="19">
-        <v>355</v>
+        <v>355.0</v>
       </c>
       <c r="E194" s="19">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B195" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C195" s="20">
         <v>0.6</v>
       </c>
       <c r="D195" s="19">
-        <v>371</v>
+        <v>371.0</v>
       </c>
       <c r="E195" s="19">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B196" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C196" s="20">
         <v>0.7</v>
       </c>
       <c r="D196" s="19">
-        <v>398</v>
+        <v>398.0</v>
       </c>
       <c r="E196" s="19">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B197" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C197" s="20">
         <v>0.79</v>
       </c>
       <c r="D197" s="19">
-        <v>422</v>
+        <v>422.0</v>
       </c>
       <c r="E197" s="19">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B198" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C198" s="20">
         <v>0.9</v>
       </c>
       <c r="D198" s="19">
-        <v>470</v>
+        <v>470.0</v>
       </c>
       <c r="E198" s="19">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>313.0</v>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B199" s="19">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C199" s="20">
         <v>0.99</v>
       </c>
       <c r="D199" s="19">
-        <v>521</v>
+        <v>521.0</v>
       </c>
       <c r="E199" s="19">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B200" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C200" s="13">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="D200" s="12">
-        <v>482</v>
+        <v>482.0</v>
       </c>
       <c r="E200" s="12">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>406.0</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B201" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C201" s="13">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="D201" s="12">
-        <v>464</v>
+        <v>464.0</v>
       </c>
       <c r="E201" s="12">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>381.0</v>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B202" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C202" s="13">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D202" s="12">
-        <v>388</v>
+        <v>388.0</v>
       </c>
       <c r="E202" s="12">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="24">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B203" s="16">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C203" s="17">
         <v>0.17</v>
       </c>
       <c r="D203" s="16">
-        <v>370</v>
+        <v>370.0</v>
       </c>
       <c r="E203" s="16">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B204" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C204" s="13">
         <v>0.25</v>
       </c>
       <c r="D204" s="12">
-        <v>376</v>
+        <v>376.0</v>
       </c>
       <c r="E204" s="12">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B205" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C205" s="13">
         <v>0.32</v>
       </c>
       <c r="D205" s="12">
-        <v>388</v>
+        <v>388.0</v>
       </c>
       <c r="E205" s="12">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B206" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C206" s="13">
         <v>0.4</v>
       </c>
       <c r="D206" s="12">
-        <v>415</v>
+        <v>415.0</v>
       </c>
       <c r="E206" s="12">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B207" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C207" s="13">
         <v>0.46</v>
       </c>
       <c r="D207" s="12">
-        <v>444</v>
+        <v>444.0</v>
       </c>
       <c r="E207" s="12">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B208" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C208" s="13">
         <v>0.54</v>
       </c>
       <c r="D208" s="12">
-        <v>468</v>
+        <v>468.0</v>
       </c>
       <c r="E208" s="12">
-        <v>315</v>
+        <v>315.0</v>
       </c>
       <c r="K208" s="4"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B209" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C209" s="13">
         <v>0.6</v>
       </c>
       <c r="D209" s="12">
-        <v>503</v>
+        <v>503.0</v>
       </c>
       <c r="E209" s="12">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="2">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B210" s="12">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C210" s="13">
         <v>0.69</v>
       </c>
       <c r="D210" s="12">
-        <v>543</v>
+        <v>543.0</v>
       </c>
       <c r="E210" s="12">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B211" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C211" s="20">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="D211" s="19">
-        <v>437</v>
+        <v>437.0</v>
       </c>
       <c r="E211" s="19">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>374.0</v>
+      </c>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B212" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C212" s="20">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="D212" s="19">
-        <v>425</v>
+        <v>425.0</v>
       </c>
       <c r="E212" s="19">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>364.0</v>
+      </c>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B213" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C213" s="20">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="D213" s="19">
-        <v>426</v>
+        <v>426.0</v>
       </c>
       <c r="E213" s="19">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346.0</v>
+      </c>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B214" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C214" s="20">
         <v>0.09</v>
       </c>
       <c r="D214" s="19">
-        <v>391</v>
+        <v>391.0</v>
       </c>
       <c r="E214" s="19">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>339.0</v>
+      </c>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="24">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B215" s="16">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C215" s="17">
         <v>0.1</v>
       </c>
       <c r="D215" s="16">
-        <v>372</v>
+        <v>372.0</v>
       </c>
       <c r="E215" s="16">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B216" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C216" s="20">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D216" s="19">
-        <v>372</v>
+        <v>372.0</v>
       </c>
       <c r="E216" s="19">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B217" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C217" s="20">
         <v>0.22</v>
       </c>
       <c r="D217" s="19">
-        <v>380</v>
+        <v>380.0</v>
       </c>
       <c r="E217" s="19">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300.0</v>
+      </c>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B218" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C218" s="20">
         <v>0.32</v>
       </c>
       <c r="D218" s="19">
-        <v>442</v>
+        <v>442.0</v>
       </c>
       <c r="E218" s="19">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="23">
-        <v>46295</v>
+        <v>46295.0</v>
       </c>
       <c r="B219" s="21">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C219" s="22">
         <v>0.44</v>
       </c>
       <c r="D219" s="21">
-        <v>514</v>
+        <v>514.0</v>
       </c>
       <c r="E219" s="21">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330.0</v>
+      </c>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="25">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B220" s="6">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C220" s="26">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="D220" s="6">
-        <v>563</v>
+        <v>563.0</v>
       </c>
       <c r="E220" s="6">
-        <v>437</v>
+        <v>437.0</v>
       </c>
       <c r="F220" s="6">
-        <v>57</v>
+        <v>57.0</v>
       </c>
       <c r="G220" s="6">
         <v>23.6</v>
@@ -4412,1554 +4394,1556 @@
       <c r="Y220" s="6"/>
       <c r="Z220" s="6"/>
     </row>
-    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B221" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C221" s="28">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="D221" s="3">
-        <v>507</v>
+        <v>507.0</v>
       </c>
       <c r="E221" s="3">
-        <v>403</v>
+        <v>403.0</v>
       </c>
       <c r="F221" s="3">
-        <v>57</v>
+        <v>57.0</v>
       </c>
       <c r="G221" s="3">
         <v>24.3</v>
       </c>
     </row>
-    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B222" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C222" s="28">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="D222" s="3">
-        <v>438</v>
+        <v>438.0</v>
       </c>
       <c r="E222" s="3">
-        <v>367</v>
+        <v>367.0</v>
       </c>
       <c r="F222" s="3">
-        <v>59</v>
+        <v>59.0</v>
       </c>
       <c r="G222" s="3">
         <v>23.3</v>
       </c>
     </row>
-    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B223" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C223" s="28">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="D223" s="3">
-        <v>411</v>
+        <v>411.0</v>
       </c>
       <c r="E223" s="3">
-        <v>349</v>
+        <v>349.0</v>
       </c>
       <c r="F223" s="3">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="G223" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B224" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C224" s="28">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="D224" s="3">
-        <v>401</v>
+        <v>401.0</v>
       </c>
       <c r="E224" s="3">
-        <v>334</v>
+        <v>334.0</v>
       </c>
       <c r="F224" s="3">
-        <v>57</v>
+        <v>57.0</v>
       </c>
       <c r="G224" s="3">
         <v>24.3</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B225" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C225" s="28">
         <v>0.1</v>
       </c>
       <c r="D225" s="3">
-        <v>385</v>
+        <v>385.0</v>
       </c>
       <c r="E225" s="3">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B226" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C226" s="28">
         <v>0.15</v>
       </c>
       <c r="D226" s="3">
-        <v>368</v>
+        <v>368.0</v>
       </c>
       <c r="E226" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B227" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C227" s="28">
         <v>0.2</v>
       </c>
       <c r="D227" s="3">
-        <v>383</v>
+        <v>383.0</v>
       </c>
       <c r="E227" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B228" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C228" s="28">
         <v>0.26</v>
       </c>
       <c r="D228" s="3">
-        <v>403</v>
+        <v>403.0</v>
       </c>
       <c r="E228" s="3">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B229" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C229" s="28">
         <v>0.35</v>
       </c>
       <c r="D229" s="3">
-        <v>446</v>
+        <v>446.0</v>
       </c>
       <c r="E229" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B230" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C230" s="28">
         <v>0.44</v>
       </c>
       <c r="D230" s="3">
-        <v>494</v>
+        <v>494.0</v>
       </c>
       <c r="E230" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B231" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="C231" s="28">
         <v>0.54</v>
       </c>
       <c r="D231" s="3">
-        <v>555</v>
+        <v>555.0</v>
       </c>
       <c r="E231" s="3">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B232" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C232" s="31">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="D232" s="30">
-        <v>550</v>
+        <v>550.0</v>
       </c>
       <c r="E232" s="30">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>421.0</v>
+      </c>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B233" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C233" s="31">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="D233" s="30">
-        <v>496</v>
+        <v>496.0</v>
       </c>
       <c r="E233" s="30">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>392.0</v>
+      </c>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B234" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C234" s="31">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="D234" s="30">
-        <v>447</v>
+        <v>447.0</v>
       </c>
       <c r="E234" s="30">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368.0</v>
+      </c>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B235" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C235" s="31">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="D235" s="30">
-        <v>411</v>
+        <v>411.0</v>
       </c>
       <c r="E235" s="30">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346.0</v>
+      </c>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B236" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C236" s="31">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="D236" s="30">
-        <v>396</v>
+        <v>396.0</v>
       </c>
       <c r="E236" s="30">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337.0</v>
+      </c>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B237" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C237" s="31">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="D237" s="30">
-        <v>401</v>
+        <v>401.0</v>
       </c>
       <c r="E237" s="30">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330.0</v>
+      </c>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="32">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B238" s="33">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C238" s="34">
         <v>0.12</v>
       </c>
       <c r="D238" s="33">
-        <v>394</v>
+        <v>394.0</v>
       </c>
       <c r="E238" s="33">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B239" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C239" s="31">
         <v>0.16</v>
       </c>
       <c r="D239" s="30">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E239" s="30">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309.0</v>
+      </c>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B240" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C240" s="31">
         <v>0.21</v>
       </c>
       <c r="D240" s="30">
-        <v>401</v>
+        <v>401.0</v>
       </c>
       <c r="E240" s="30">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B241" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C241" s="31">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="D241" s="30">
-        <v>444</v>
+        <v>444.0</v>
       </c>
       <c r="E241" s="30">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B242" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C242" s="31">
         <v>0.39</v>
       </c>
       <c r="D242" s="30">
-        <v>518</v>
+        <v>518.0</v>
       </c>
       <c r="E242" s="30">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="29">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B243" s="30">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="C243" s="31">
         <v>0.43</v>
       </c>
       <c r="D243" s="30">
-        <v>541</v>
+        <v>541.0</v>
       </c>
       <c r="E243" s="30">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B244" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C244" s="28">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="D244" s="3">
-        <v>548</v>
+        <v>548.0</v>
       </c>
       <c r="E244" s="3">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>426.0</v>
+      </c>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B245" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C245" s="28">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="D245" s="3">
-        <v>457</v>
+        <v>457.0</v>
       </c>
       <c r="E245" s="3">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>381.0</v>
+      </c>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B246" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C246" s="28">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="D246" s="3">
-        <v>427</v>
+        <v>427.0</v>
       </c>
       <c r="E246" s="3">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>358.0</v>
+      </c>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B247" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C247" s="28">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="D247" s="3">
-        <v>421</v>
+        <v>421.0</v>
       </c>
       <c r="E247" s="3">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>347.0</v>
+      </c>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B248" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C248" s="28">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="D248" s="3">
-        <v>402</v>
+        <v>402.0</v>
       </c>
       <c r="E248" s="3">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337.0</v>
+      </c>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B249" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C249" s="28">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="D249" s="3">
-        <v>417</v>
+        <v>417.0</v>
       </c>
       <c r="E249" s="3">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>332.0</v>
+      </c>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B250" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C250" s="28">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="D250" s="3">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E250" s="3">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327.0</v>
+      </c>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B251" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C251" s="28">
         <v>0.11</v>
       </c>
       <c r="D251" s="3">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E251" s="3">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B252" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C252" s="28">
         <v>0.19</v>
       </c>
       <c r="D252" s="3">
-        <v>419</v>
+        <v>419.0</v>
       </c>
       <c r="E252" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B253" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C253" s="28">
         <v>0.25</v>
       </c>
       <c r="D253" s="3">
-        <v>462</v>
+        <v>462.0</v>
       </c>
       <c r="E253" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B254" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C254" s="28">
         <v>0.36</v>
       </c>
       <c r="D254" s="3">
-        <v>534</v>
+        <v>534.0</v>
       </c>
       <c r="E254" s="3">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B255" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C255" s="28">
         <v>0.16</v>
       </c>
       <c r="D255" s="3">
-        <v>532</v>
+        <v>532.0</v>
       </c>
       <c r="E255" s="3">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>433.0</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B256" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C256" s="28">
         <v>0.23</v>
       </c>
       <c r="D256" s="3">
-        <v>399</v>
+        <v>399.0</v>
       </c>
       <c r="E256" s="3">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>345.0</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B257" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C257" s="28">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="D257" s="3">
-        <v>372</v>
+        <v>372.0</v>
       </c>
       <c r="E257" s="3">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324.0</v>
+      </c>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B258" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C258" s="28">
         <v>0.32</v>
       </c>
       <c r="D258" s="3">
-        <v>353</v>
+        <v>353.0</v>
       </c>
       <c r="E258" s="3">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311.0</v>
+      </c>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B259" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C259" s="28">
         <v>0.35</v>
       </c>
       <c r="D259" s="3">
-        <v>350</v>
+        <v>350.0</v>
       </c>
       <c r="E259" s="3">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B260" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C260" s="28">
         <v>0.42</v>
       </c>
       <c r="D260" s="3">
-        <v>351</v>
+        <v>351.0</v>
       </c>
       <c r="E260" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B261" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C261" s="28">
         <v>0.47</v>
       </c>
       <c r="D261" s="3">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="E261" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B262" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C262" s="28">
-        <v>0.56000000000000005</v>
+        <v>0.56</v>
       </c>
       <c r="D262" s="3">
-        <v>369</v>
+        <v>369.0</v>
       </c>
       <c r="E262" s="3">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B263" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C263" s="28">
         <v>0.65</v>
       </c>
       <c r="D263" s="3">
-        <v>384</v>
+        <v>384.0</v>
       </c>
       <c r="E263" s="3">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B264" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C264" s="28">
         <v>0.74</v>
       </c>
       <c r="D264" s="3">
-        <v>418</v>
+        <v>418.0</v>
       </c>
       <c r="E264" s="3">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>312.0</v>
+      </c>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B265" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C265" s="28">
         <v>0.83</v>
       </c>
       <c r="D265" s="3">
-        <v>442</v>
+        <v>442.0</v>
       </c>
       <c r="E265" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="27">
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="B266" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="C266" s="28">
         <v>0.93</v>
       </c>
       <c r="D266" s="3">
-        <v>482</v>
+        <v>482.0</v>
       </c>
       <c r="E266" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="27"/>
     </row>
-    <row r="268" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="27"/>
     </row>
-    <row r="269" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="27"/>
     </row>
-    <row r="270" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="+HZbGVJqjjHP6FmRYHuoZrb9uV+t2n2MWgGA4K0nFaw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sSqulxmff5jct3tHkwnrlsOw0sLhTPijtkysnhKKNX4="/>
     </ext>
   </extLst>
 </workbook>
@@ -43,10 +43,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm"/>
+    <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -74,6 +75,11 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -169,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -231,6 +237,40 @@
     <xf borderId="6" fillId="2" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="11" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="11" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -4997,272 +5037,1064 @@
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="27">
+      <c r="A255" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B255" s="3">
+      <c r="B255" s="36">
         <v>10.0</v>
       </c>
-      <c r="C255" s="28">
+      <c r="C255" s="37">
         <v>0.16</v>
       </c>
-      <c r="D255" s="3">
+      <c r="D255" s="36">
         <v>532.0</v>
       </c>
-      <c r="E255" s="3">
+      <c r="E255" s="36">
         <v>433.0</v>
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="27">
+      <c r="A256" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B256" s="3">
+      <c r="B256" s="36">
         <v>10.0</v>
       </c>
-      <c r="C256" s="28">
+      <c r="C256" s="37">
         <v>0.23</v>
       </c>
-      <c r="D256" s="3">
+      <c r="D256" s="36">
         <v>399.0</v>
       </c>
-      <c r="E256" s="3">
+      <c r="E256" s="36">
         <v>345.0</v>
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="27">
+      <c r="A257" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B257" s="3">
+      <c r="B257" s="36">
         <v>10.0</v>
       </c>
-      <c r="C257" s="28">
+      <c r="C257" s="37">
         <v>0.28</v>
       </c>
-      <c r="D257" s="3">
+      <c r="D257" s="36">
         <v>372.0</v>
       </c>
-      <c r="E257" s="3">
+      <c r="E257" s="36">
         <v>324.0</v>
       </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="27">
+      <c r="A258" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B258" s="3">
+      <c r="B258" s="36">
         <v>10.0</v>
       </c>
-      <c r="C258" s="28">
+      <c r="C258" s="37">
         <v>0.32</v>
       </c>
-      <c r="D258" s="3">
+      <c r="D258" s="36">
         <v>353.0</v>
       </c>
-      <c r="E258" s="3">
+      <c r="E258" s="36">
         <v>311.0</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="27">
+      <c r="A259" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B259" s="3">
+      <c r="B259" s="36">
         <v>10.0</v>
       </c>
-      <c r="C259" s="28">
+      <c r="C259" s="37">
         <v>0.35</v>
       </c>
-      <c r="D259" s="3">
+      <c r="D259" s="36">
         <v>350.0</v>
       </c>
-      <c r="E259" s="3">
+      <c r="E259" s="36">
         <v>310.0</v>
       </c>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="27">
+      <c r="A260" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B260" s="3">
+      <c r="B260" s="36">
         <v>10.0</v>
       </c>
-      <c r="C260" s="28">
+      <c r="C260" s="37">
         <v>0.42</v>
       </c>
-      <c r="D260" s="3">
+      <c r="D260" s="36">
         <v>351.0</v>
       </c>
-      <c r="E260" s="3">
+      <c r="E260" s="36">
         <v>308.0</v>
       </c>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="27">
+      <c r="A261" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B261" s="3">
+      <c r="B261" s="36">
         <v>10.0</v>
       </c>
-      <c r="C261" s="28">
+      <c r="C261" s="37">
         <v>0.47</v>
       </c>
-      <c r="D261" s="3">
+      <c r="D261" s="36">
         <v>363.0</v>
       </c>
-      <c r="E261" s="3">
+      <c r="E261" s="36">
         <v>308.0</v>
       </c>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="27">
+      <c r="A262" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B262" s="3">
+      <c r="B262" s="36">
         <v>10.0</v>
       </c>
-      <c r="C262" s="28">
+      <c r="C262" s="37">
         <v>0.56</v>
       </c>
-      <c r="D262" s="3">
+      <c r="D262" s="36">
         <v>369.0</v>
       </c>
-      <c r="E262" s="3">
+      <c r="E262" s="36">
         <v>304.0</v>
       </c>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="27">
+      <c r="A263" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B263" s="3">
+      <c r="B263" s="36">
         <v>10.0</v>
       </c>
-      <c r="C263" s="28">
+      <c r="C263" s="37">
         <v>0.65</v>
       </c>
-      <c r="D263" s="3">
+      <c r="D263" s="36">
         <v>384.0</v>
       </c>
-      <c r="E263" s="3">
+      <c r="E263" s="36">
         <v>307.0</v>
       </c>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="27">
+      <c r="A264" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B264" s="3">
+      <c r="B264" s="36">
         <v>10.0</v>
       </c>
-      <c r="C264" s="28">
+      <c r="C264" s="37">
         <v>0.74</v>
       </c>
-      <c r="D264" s="3">
+      <c r="D264" s="36">
         <v>418.0</v>
       </c>
-      <c r="E264" s="3">
+      <c r="E264" s="36">
         <v>312.0</v>
       </c>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="27">
+      <c r="A265" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B265" s="3">
+      <c r="B265" s="36">
         <v>10.0</v>
       </c>
-      <c r="C265" s="28">
+      <c r="C265" s="37">
         <v>0.83</v>
       </c>
-      <c r="D265" s="3">
+      <c r="D265" s="36">
         <v>442.0</v>
       </c>
-      <c r="E265" s="3">
+      <c r="E265" s="36">
         <v>306.0</v>
       </c>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="27">
+      <c r="A266" s="35">
         <v>46301.0</v>
       </c>
-      <c r="B266" s="3">
+      <c r="B266" s="36">
         <v>10.0</v>
       </c>
-      <c r="C266" s="28">
+      <c r="C266" s="37">
         <v>0.93</v>
       </c>
-      <c r="D266" s="3">
+      <c r="D266" s="36">
         <v>482.0</v>
       </c>
-      <c r="E266" s="3">
+      <c r="E266" s="36">
         <v>320.0</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="27"/>
+      <c r="A267" s="38">
+        <v>46308.0</v>
+      </c>
+      <c r="B267" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="C267" s="40">
+        <v>0.14</v>
+      </c>
+      <c r="D267" s="39">
+        <v>601.0</v>
+      </c>
+      <c r="E267" s="39">
+        <v>490.0</v>
+      </c>
+      <c r="F267" s="39">
+        <v>67.0</v>
+      </c>
+      <c r="G267" s="39">
+        <v>20.2</v>
+      </c>
+      <c r="H267" s="41"/>
+      <c r="I267" s="41"/>
+      <c r="J267" s="41"/>
+      <c r="K267" s="41"/>
+      <c r="L267" s="41"/>
+      <c r="M267" s="41"/>
+      <c r="N267" s="41"/>
+      <c r="O267" s="41"/>
+      <c r="P267" s="41"/>
+      <c r="Q267" s="41"/>
+      <c r="R267" s="41"/>
+      <c r="S267" s="41"/>
+      <c r="T267" s="41"/>
+      <c r="U267" s="41"/>
+      <c r="V267" s="41"/>
+      <c r="W267" s="41"/>
+      <c r="X267" s="41"/>
+      <c r="Y267" s="41"/>
+      <c r="Z267" s="41"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="27"/>
+      <c r="A268" s="42">
+        <v>46308.0</v>
+      </c>
+      <c r="B268" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C268" s="44">
+        <v>0.19</v>
+      </c>
+      <c r="D268" s="43">
+        <v>446.0</v>
+      </c>
+      <c r="E268" s="43">
+        <v>379.0</v>
+      </c>
+      <c r="F268" s="43">
+        <v>65.0</v>
+      </c>
+      <c r="G268" s="43">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="27"/>
-    </row>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
+      <c r="A269" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B269" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C269" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="D269" s="43">
+        <v>403.0</v>
+      </c>
+      <c r="E269" s="43">
+        <v>350.0</v>
+      </c>
+      <c r="F269" s="43">
+        <v>64.0</v>
+      </c>
+      <c r="G269" s="43">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="A270" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B270" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C270" s="44">
+        <v>0.26</v>
+      </c>
+      <c r="D270" s="43">
+        <v>371.0</v>
+      </c>
+      <c r="E270" s="43">
+        <v>324.0</v>
+      </c>
+      <c r="F270" s="43">
+        <v>64.0</v>
+      </c>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="A271" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B271" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C271" s="44">
+        <v>0.29</v>
+      </c>
+      <c r="D271" s="43">
+        <v>360.0</v>
+      </c>
+      <c r="E271" s="43">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="A272" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B272" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C272" s="44">
+        <v>0.33</v>
+      </c>
+      <c r="D272" s="43">
+        <v>353.0</v>
+      </c>
+      <c r="E272" s="43">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="A273" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B273" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C273" s="44">
+        <v>0.38</v>
+      </c>
+      <c r="D273" s="43">
+        <v>350.0</v>
+      </c>
+      <c r="E273" s="43">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="A274" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B274" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C274" s="44">
+        <v>0.42</v>
+      </c>
+      <c r="D274" s="43">
+        <v>350.0</v>
+      </c>
+      <c r="E274" s="43">
+        <v>301.0</v>
+      </c>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="A275" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B275" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C275" s="44">
+        <v>0.48</v>
+      </c>
+      <c r="D275" s="43">
+        <v>351.0</v>
+      </c>
+      <c r="E275" s="43">
+        <v>300.0</v>
+      </c>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="A276" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B276" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C276" s="44">
+        <v>0.54</v>
+      </c>
+      <c r="D276" s="43">
+        <v>361.0</v>
+      </c>
+      <c r="E276" s="43">
+        <v>302.0</v>
+      </c>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="A277" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B277" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C277" s="44">
+        <v>0.61</v>
+      </c>
+      <c r="D277" s="43">
+        <v>370.0</v>
+      </c>
+      <c r="E277" s="43">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="A278" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B278" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C278" s="44">
+        <v>0.66</v>
+      </c>
+      <c r="D278" s="43">
+        <v>387.0</v>
+      </c>
+      <c r="E278" s="43">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="A279" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B279" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C279" s="44">
+        <v>0.71</v>
+      </c>
+      <c r="D279" s="43">
+        <v>395.0</v>
+      </c>
+      <c r="E279" s="43">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="A280" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B280" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C280" s="44">
+        <v>0.8</v>
+      </c>
+      <c r="D280" s="43">
+        <v>423.0</v>
+      </c>
+      <c r="E280" s="43">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="A281" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B281" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C281" s="44">
+        <v>0.86</v>
+      </c>
+      <c r="D281" s="43">
+        <v>442.0</v>
+      </c>
+      <c r="E281" s="43">
+        <v>307.0</v>
+      </c>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="A282" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B282" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="C282" s="44">
+        <v>0.94</v>
+      </c>
+      <c r="D282" s="43">
+        <v>489.0</v>
+      </c>
+      <c r="E282" s="43">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="A283" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B283" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C283" s="48">
+        <v>0.083</v>
+      </c>
+      <c r="D283" s="47">
+        <v>551.0</v>
+      </c>
+      <c r="E283" s="47">
+        <v>453.0</v>
+      </c>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="A284" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B284" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C284" s="48">
+        <v>0.087</v>
+      </c>
+      <c r="D284" s="47">
+        <v>505.0</v>
+      </c>
+      <c r="E284" s="47">
+        <v>420.0</v>
+      </c>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="A285" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B285" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C285" s="48">
+        <v>0.094</v>
+      </c>
+      <c r="D285" s="47">
+        <v>463.0</v>
+      </c>
+      <c r="E285" s="47">
+        <v>397.0</v>
+      </c>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="A286" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B286" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C286" s="48">
+        <v>0.098</v>
+      </c>
+      <c r="D286" s="47">
+        <v>454.0</v>
+      </c>
+      <c r="E286" s="47">
+        <v>386.0</v>
+      </c>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="A287" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B287" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C287" s="48">
+        <v>0.12</v>
+      </c>
+      <c r="D287" s="47">
+        <v>394.0</v>
+      </c>
+      <c r="E287" s="47">
+        <v>346.0</v>
+      </c>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="A288" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B288" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C288" s="48">
+        <v>0.16</v>
+      </c>
+      <c r="D288" s="47">
+        <v>362.0</v>
+      </c>
+      <c r="E288" s="47">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="A289" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B289" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C289" s="48">
+        <v>0.19</v>
+      </c>
+      <c r="D289" s="47">
+        <v>359.0</v>
+      </c>
+      <c r="E289" s="47">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="A290" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B290" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C290" s="48">
+        <v>0.25</v>
+      </c>
+      <c r="D290" s="47">
+        <v>365.0</v>
+      </c>
+      <c r="E290" s="47">
+        <v>306.0</v>
+      </c>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="A291" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B291" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C291" s="48">
+        <v>0.28</v>
+      </c>
+      <c r="D291" s="47">
+        <v>367.0</v>
+      </c>
+      <c r="E291" s="47">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="A292" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B292" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C292" s="48">
+        <v>0.33</v>
+      </c>
+      <c r="D292" s="47">
+        <v>385.0</v>
+      </c>
+      <c r="E292" s="47">
+        <v>304.0</v>
+      </c>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="A293" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B293" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C293" s="48">
+        <v>0.4</v>
+      </c>
+      <c r="D293" s="47">
+        <v>398.0</v>
+      </c>
+      <c r="E293" s="47">
+        <v>303.0</v>
+      </c>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="A294" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B294" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C294" s="48">
+        <v>0.46</v>
+      </c>
+      <c r="D294" s="47">
+        <v>423.0</v>
+      </c>
+      <c r="E294" s="47">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="A295" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B295" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C295" s="48">
+        <v>0.52</v>
+      </c>
+      <c r="D295" s="47">
+        <v>462.0</v>
+      </c>
+      <c r="E295" s="47">
+        <v>311.0</v>
+      </c>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="A296" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B296" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C296" s="48">
+        <v>0.57</v>
+      </c>
+      <c r="D296" s="47">
+        <v>472.0</v>
+      </c>
+      <c r="E296" s="47">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="A297" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B297" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C297" s="48">
+        <v>0.65</v>
+      </c>
+      <c r="D297" s="47">
+        <v>501.0</v>
+      </c>
+      <c r="E297" s="47">
+        <v>324.0</v>
+      </c>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="A298" s="46">
+        <v>46308.0</v>
+      </c>
+      <c r="B298" s="47">
+        <v>20.0</v>
+      </c>
+      <c r="C298" s="48">
+        <v>0.74</v>
+      </c>
+      <c r="D298" s="47">
+        <v>529.0</v>
+      </c>
+      <c r="E298" s="47">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="A299" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B299" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C299" s="44">
+        <v>0.054</v>
+      </c>
+      <c r="D299" s="43">
+        <v>590.0</v>
+      </c>
+      <c r="E299" s="43">
+        <v>552.0</v>
+      </c>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="A300" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B300" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C300" s="44">
+        <v>0.059</v>
+      </c>
+      <c r="D300" s="43">
+        <v>513.0</v>
+      </c>
+      <c r="E300" s="43">
+        <v>418.0</v>
+      </c>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="A301" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B301" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C301" s="44">
+        <v>0.062</v>
+      </c>
+      <c r="D301" s="43">
+        <v>472.0</v>
+      </c>
+      <c r="E301" s="43">
+        <v>399.0</v>
+      </c>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="A302" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B302" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C302" s="44">
+        <v>0.066</v>
+      </c>
+      <c r="D302" s="43">
+        <v>473.0</v>
+      </c>
+      <c r="E302" s="43">
+        <v>386.0</v>
+      </c>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="A303" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B303" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C303" s="44">
+        <v>0.078</v>
+      </c>
+      <c r="D303" s="43">
+        <v>402.0</v>
+      </c>
+      <c r="E303" s="43">
+        <v>355.0</v>
+      </c>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="A304" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B304" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C304" s="44">
+        <v>0.086</v>
+      </c>
+      <c r="D304" s="43">
+        <v>421.0</v>
+      </c>
+      <c r="E304" s="43">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="A305" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B305" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C305" s="44">
+        <v>0.093</v>
+      </c>
+      <c r="D305" s="43">
+        <v>409.0</v>
+      </c>
+      <c r="E305" s="43">
+        <v>339.0</v>
+      </c>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="A306" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B306" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C306" s="44">
+        <v>0.14</v>
+      </c>
+      <c r="D306" s="43">
+        <v>341.0</v>
+      </c>
+      <c r="E306" s="43">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="A307" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B307" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C307" s="44">
+        <v>0.23</v>
+      </c>
+      <c r="D307" s="43">
+        <v>393.0</v>
+      </c>
+      <c r="E307" s="43">
+        <v>308.0</v>
+      </c>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="A308" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B308" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C308" s="44">
+        <v>0.27</v>
+      </c>
+      <c r="D308" s="43">
+        <v>412.0</v>
+      </c>
+      <c r="E308" s="43">
+        <v>305.0</v>
+      </c>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="A309" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B309" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C309" s="44">
+        <v>0.37</v>
+      </c>
+      <c r="D309" s="43">
+        <v>455.0</v>
+      </c>
+      <c r="E309" s="43">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="A310" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B310" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C310" s="44">
+        <v>0.41</v>
+      </c>
+      <c r="D310" s="43">
+        <v>481.0</v>
+      </c>
+      <c r="E310" s="43">
+        <v>322.0</v>
+      </c>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="A311" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B311" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C311" s="44">
+        <v>0.46</v>
+      </c>
+      <c r="D311" s="43">
+        <v>521.0</v>
+      </c>
+      <c r="E311" s="43">
+        <v>321.0</v>
+      </c>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="A312" s="45">
+        <v>46308.0</v>
+      </c>
+      <c r="B312" s="43">
+        <v>30.0</v>
+      </c>
+      <c r="C312" s="44">
+        <v>0.56</v>
+      </c>
+      <c r="D312" s="43">
+        <v>590.0</v>
+      </c>
+      <c r="E312" s="43">
+        <v>328.0</v>
+      </c>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="A313" s="45"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="A314" s="45"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="A315" s="45"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="A316" s="45"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="A317" s="45"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="A318" s="45"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="A319" s="45"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="A320" s="45"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="A321" s="45"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="A322" s="45"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="A323" s="45"/>
+    </row>
     <row r="324" ht="15.75" customHeight="1"/>
     <row r="325" ht="15.75" customHeight="1"/>
     <row r="326" ht="15.75" customHeight="1"/>
@@ -5923,23 +6755,6 @@
     <row r="981" ht="15.75" customHeight="1"/>
     <row r="982" ht="15.75" customHeight="1"/>
     <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
